--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01759042-EC1B-49E1-B108-0FD36F6C8E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06BFBBC-44C0-4663-8331-30591A928105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="885" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="1260" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -11350,7 +11350,7 @@
         <v>7</v>
       </c>
       <c r="O5" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="P5" s="2">
         <v>0</v>
@@ -27326,7 +27326,7 @@
         <v>7</v>
       </c>
       <c r="O5" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="P5" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06BFBBC-44C0-4663-8331-30591A928105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5283F8-77BC-4C79-A33F-A63FB4F27482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="1260" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -12202,7 +12202,7 @@
         <v>7</v>
       </c>
       <c r="O11" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="P11" s="2">
         <v>0</v>
@@ -13764,7 +13764,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="2">
-        <v>950</v>
+        <v>850</v>
       </c>
       <c r="P22" s="2">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>1</v>
       </c>
       <c r="N32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O32" s="2">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="P32" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5283F8-77BC-4C79-A33F-A63FB4F27482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09438CB3-6371-4A4D-B43B-9FD219F04E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1875" yWindow="870" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -14912,7 +14912,7 @@
         <v>0</v>
       </c>
       <c r="S30" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T30" s="2">
         <v>0</v>
@@ -14924,7 +14924,7 @@
         <v>0</v>
       </c>
       <c r="W30" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="X30" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09438CB3-6371-4A4D-B43B-9FD219F04E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65218C8F-A3E6-4F32-9CA7-2E6A0BDF405A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="870" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2490" yWindow="870" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3727" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3740" uniqueCount="305">
   <si>
     <t>desc</t>
   </si>
@@ -2563,6 +2563,37 @@
   </si>
   <si>
     <t>a_FrozenFruits</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>strawberry_sponge_cake</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ショートケーキの納品</t>
+    <rPh sb="8" eb="10">
+      <t>ノウヒン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;メイド学校の先生&lt;/color&gt;の方からのご依頼ね。
+来賓客をもてなすためにおいしいケーキがほしいそうよ。</t>
+    <rPh sb="22" eb="24">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>ライヒンキャク</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -10712,7 +10743,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AT58"/>
+  <dimension ref="A1:AT59"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
@@ -10880,7 +10911,7 @@
     </row>
     <row r="2" spans="1:46" s="10" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
-        <f t="shared" ref="A2:A58" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A59" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="7">
@@ -11168,7 +11199,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <f t="shared" ref="B4:B58" si="1">(ROW()-2)+10000</f>
+        <f t="shared" ref="B4:B59" si="1">(ROW()-2)+10000</f>
         <v>10002</v>
       </c>
       <c r="C4" s="2">
@@ -15160,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>39</v>
+        <v>281</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>281</v>
@@ -16148,22 +16179,22 @@
         <v>0</v>
       </c>
       <c r="E39" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>160</v>
+        <v>302</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>293</v>
+        <v>7</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>294</v>
+        <v>7</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>7</v>
@@ -16178,25 +16209,25 @@
         <v>2</v>
       </c>
       <c r="O39" s="2">
-        <v>450</v>
+        <v>1500</v>
       </c>
       <c r="P39" s="2">
         <v>0</v>
       </c>
       <c r="Q39" s="2">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="R39" s="2">
         <v>0</v>
       </c>
       <c r="S39" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T39" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U39" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="V39" s="2">
         <v>0</v>
@@ -16214,7 +16245,7 @@
         <v>0</v>
       </c>
       <c r="AA39" s="2">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AB39" s="2">
         <v>0</v>
@@ -16262,13 +16293,13 @@
         <v>10</v>
       </c>
       <c r="AQ39" s="14" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="AR39" s="5" t="s">
-        <v>183</v>
+        <v>303</v>
       </c>
       <c r="AS39" s="4" t="s">
-        <v>202</v>
+        <v>304</v>
       </c>
       <c r="AT39" s="2">
         <v>0</v>
@@ -16296,16 +16327,16 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>7</v>
+        <v>293</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>7</v>
+        <v>294</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>7</v>
@@ -16326,13 +16357,13 @@
         <v>0</v>
       </c>
       <c r="Q40" s="2">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="R40" s="2">
         <v>0</v>
       </c>
       <c r="S40" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T40" s="2">
         <v>50</v>
@@ -16404,13 +16435,13 @@
         <v>10</v>
       </c>
       <c r="AQ40" s="14" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="AR40" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AS40" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AT40" s="2">
         <v>0</v>
@@ -16438,10 +16469,10 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>7</v>
@@ -16462,25 +16493,25 @@
         <v>2</v>
       </c>
       <c r="O41" s="2">
-        <v>1100</v>
+        <v>450</v>
       </c>
       <c r="P41" s="2">
         <v>0</v>
       </c>
       <c r="Q41" s="2">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="R41" s="2">
         <v>0</v>
       </c>
       <c r="S41" s="2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="T41" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U41" s="2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2">
         <v>0</v>
@@ -16498,7 +16529,7 @@
         <v>0</v>
       </c>
       <c r="AA41" s="2">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="AB41" s="2">
         <v>0</v>
@@ -16546,13 +16577,13 @@
         <v>10</v>
       </c>
       <c r="AQ41" s="14" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="AR41" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AS41" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="AT41" s="2">
         <v>0</v>
@@ -16568,22 +16599,22 @@
         <v>10040</v>
       </c>
       <c r="C42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
       </c>
       <c r="E42" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F42" s="2">
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>39</v>
+        <v>220</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>7</v>
+        <v>162</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>7</v>
@@ -16592,7 +16623,7 @@
         <v>7</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>301</v>
+        <v>7</v>
       </c>
       <c r="L42" s="2">
         <v>0</v>
@@ -16601,28 +16632,28 @@
         <v>1</v>
       </c>
       <c r="N42" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O42" s="2">
-        <v>350</v>
+        <v>1100</v>
       </c>
       <c r="P42" s="2">
         <v>0</v>
       </c>
       <c r="Q42" s="2">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="R42" s="2">
         <v>0</v>
       </c>
       <c r="S42" s="2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="T42" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="U42" s="2">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="V42" s="2">
         <v>0</v>
@@ -16640,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="AA42" s="2">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AB42" s="2">
         <v>0</v>
@@ -16688,13 +16719,13 @@
         <v>10</v>
       </c>
       <c r="AQ42" s="14" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="AR42" s="5" t="s">
-        <v>299</v>
+        <v>185</v>
       </c>
       <c r="AS42" s="4" t="s">
-        <v>283</v>
+        <v>208</v>
       </c>
       <c r="AT42" s="2">
         <v>0</v>
@@ -16710,7 +16741,7 @@
         <v>10041</v>
       </c>
       <c r="C43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
@@ -16722,7 +16753,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>163</v>
+        <v>39</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>7</v>
@@ -16734,7 +16765,7 @@
         <v>7</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>177</v>
+        <v>301</v>
       </c>
       <c r="L43" s="2">
         <v>0</v>
@@ -16743,16 +16774,16 @@
         <v>1</v>
       </c>
       <c r="N43" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O43" s="2">
-        <v>1500</v>
+        <v>350</v>
       </c>
       <c r="P43" s="2">
         <v>0</v>
       </c>
       <c r="Q43" s="2">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="R43" s="2">
         <v>0</v>
@@ -16761,10 +16792,10 @@
         <v>0</v>
       </c>
       <c r="T43" s="2">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U43" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2">
         <v>0</v>
@@ -16782,7 +16813,7 @@
         <v>0</v>
       </c>
       <c r="AA43" s="2">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AB43" s="2">
         <v>0</v>
@@ -16818,7 +16849,7 @@
         <v>0</v>
       </c>
       <c r="AM43" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AN43" s="2">
         <v>0</v>
@@ -16833,10 +16864,10 @@
         <v>266</v>
       </c>
       <c r="AR43" s="5" t="s">
-        <v>186</v>
+        <v>299</v>
       </c>
       <c r="AS43" s="4" t="s">
-        <v>204</v>
+        <v>283</v>
       </c>
       <c r="AT43" s="2">
         <v>0</v>
@@ -16864,19 +16895,19 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>223</v>
+        <v>163</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>176</v>
+        <v>7</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>298</v>
+        <v>7</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>7</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="L44" s="2">
         <v>0</v>
@@ -16888,44 +16919,44 @@
         <v>2</v>
       </c>
       <c r="O44" s="2">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="P44" s="2">
         <v>0</v>
       </c>
       <c r="Q44" s="2">
+        <v>77</v>
+      </c>
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2">
+        <v>0</v>
+      </c>
+      <c r="U44" s="2">
         <v>80</v>
       </c>
-      <c r="R44" s="2">
-        <v>0</v>
-      </c>
-      <c r="S44" s="2">
-        <v>0</v>
-      </c>
-      <c r="T44" s="2">
+      <c r="V44" s="2">
+        <v>0</v>
+      </c>
+      <c r="W44" s="2">
+        <v>0</v>
+      </c>
+      <c r="X44" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="2">
         <v>80</v>
       </c>
-      <c r="U44" s="2">
-        <v>0</v>
-      </c>
-      <c r="V44" s="2">
-        <v>0</v>
-      </c>
-      <c r="W44" s="2">
-        <v>0</v>
-      </c>
-      <c r="X44" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="2">
-        <v>50</v>
-      </c>
       <c r="AB44" s="2">
         <v>0</v>
       </c>
@@ -16960,7 +16991,7 @@
         <v>0</v>
       </c>
       <c r="AM44" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AN44" s="2">
         <v>0</v>
@@ -16972,13 +17003,13 @@
         <v>10</v>
       </c>
       <c r="AQ44" s="14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AR44" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AS44" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AT44" s="2">
         <v>0</v>
@@ -17006,16 +17037,16 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>296</v>
+        <v>7</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>7</v>
@@ -17036,7 +17067,7 @@
         <v>0</v>
       </c>
       <c r="Q45" s="2">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="R45" s="2">
         <v>0</v>
@@ -17045,7 +17076,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="2">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U45" s="2">
         <v>0</v>
@@ -17063,11 +17094,11 @@
         <v>0</v>
       </c>
       <c r="Z45" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="2">
         <v>50</v>
       </c>
-      <c r="AA45" s="2">
-        <v>70</v>
-      </c>
       <c r="AB45" s="2">
         <v>0</v>
       </c>
@@ -17102,7 +17133,7 @@
         <v>0</v>
       </c>
       <c r="AM45" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AN45" s="2">
         <v>0</v>
@@ -17114,13 +17145,13 @@
         <v>10</v>
       </c>
       <c r="AQ45" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AR45" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AS45" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AT45" s="2">
         <v>0</v>
@@ -17148,16 +17179,16 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>7</v>
+        <v>296</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>7</v>
@@ -17172,7 +17203,7 @@
         <v>2</v>
       </c>
       <c r="O46" s="2">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P46" s="2">
         <v>0</v>
@@ -17205,7 +17236,7 @@
         <v>0</v>
       </c>
       <c r="Z46" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AA46" s="2">
         <v>70</v>
@@ -17259,10 +17290,10 @@
         <v>265</v>
       </c>
       <c r="AR46" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AS46" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT46" s="2">
         <v>0</v>
@@ -17290,13 +17321,13 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>7</v>
+        <v>297</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>7</v>
@@ -17314,22 +17345,22 @@
         <v>2</v>
       </c>
       <c r="O47" s="2">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="P47" s="2">
         <v>0</v>
       </c>
       <c r="Q47" s="2">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="R47" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="S47" s="2">
         <v>0</v>
       </c>
       <c r="T47" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U47" s="2">
         <v>0</v>
@@ -17347,10 +17378,10 @@
         <v>0</v>
       </c>
       <c r="Z47" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA47" s="2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AB47" s="2">
         <v>0</v>
@@ -17398,13 +17429,13 @@
         <v>10</v>
       </c>
       <c r="AQ47" s="14" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AR47" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AS47" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AT47" s="2">
         <v>0</v>
@@ -17432,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>7</v>
@@ -17456,28 +17487,28 @@
         <v>2</v>
       </c>
       <c r="O48" s="2">
-        <v>3500</v>
+        <v>850</v>
       </c>
       <c r="P48" s="2">
         <v>0</v>
       </c>
       <c r="Q48" s="2">
-        <v>330</v>
+        <v>32</v>
       </c>
       <c r="R48" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="S48" s="2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="T48" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U48" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V48" s="2">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="W48" s="2">
         <v>0</v>
@@ -17492,7 +17523,7 @@
         <v>0</v>
       </c>
       <c r="AA48" s="2">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AB48" s="2">
         <v>0</v>
@@ -17528,7 +17559,7 @@
         <v>0</v>
       </c>
       <c r="AM48" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AN48" s="2">
         <v>0</v>
@@ -17540,13 +17571,13 @@
         <v>10</v>
       </c>
       <c r="AQ48" s="14" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="AR48" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AS48" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AT48" s="2">
         <v>0</v>
@@ -17574,10 +17605,10 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>7</v>
@@ -17598,28 +17629,28 @@
         <v>2</v>
       </c>
       <c r="O49" s="2">
-        <v>500</v>
+        <v>3500</v>
       </c>
       <c r="P49" s="2">
         <v>0</v>
       </c>
       <c r="Q49" s="2">
-        <v>32</v>
+        <v>330</v>
       </c>
       <c r="R49" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S49" s="2">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="T49" s="2">
+        <v>0</v>
+      </c>
+      <c r="U49" s="2">
         <v>60</v>
       </c>
-      <c r="U49" s="2">
-        <v>20</v>
-      </c>
       <c r="V49" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W49" s="2">
         <v>0</v>
@@ -17634,7 +17665,7 @@
         <v>0</v>
       </c>
       <c r="AA49" s="2">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AB49" s="2">
         <v>0</v>
@@ -17670,7 +17701,7 @@
         <v>0</v>
       </c>
       <c r="AM49" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AN49" s="2">
         <v>0</v>
@@ -17682,13 +17713,13 @@
         <v>10</v>
       </c>
       <c r="AQ49" s="14" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="AR49" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AS49" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AT49" s="2">
         <v>0</v>
@@ -17716,10 +17747,10 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>7</v>
@@ -17740,13 +17771,13 @@
         <v>2</v>
       </c>
       <c r="O50" s="2">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P50" s="2">
         <v>0</v>
       </c>
       <c r="Q50" s="2">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="R50" s="2">
         <v>0</v>
@@ -17755,10 +17786,10 @@
         <v>0</v>
       </c>
       <c r="T50" s="2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="U50" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V50" s="2">
         <v>0</v>
@@ -17782,7 +17813,7 @@
         <v>0</v>
       </c>
       <c r="AC50" s="3" t="s">
-        <v>178</v>
+        <v>7</v>
       </c>
       <c r="AD50" s="3" t="s">
         <v>7</v>
@@ -17797,7 +17828,7 @@
         <v>7</v>
       </c>
       <c r="AH50" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI50" s="2">
         <v>0</v>
@@ -17824,13 +17855,13 @@
         <v>10</v>
       </c>
       <c r="AQ50" s="14" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AR50" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AS50" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AT50" s="2">
         <v>0</v>
@@ -17858,10 +17889,10 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>7</v>
@@ -17924,7 +17955,7 @@
         <v>0</v>
       </c>
       <c r="AC51" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AD51" s="3" t="s">
         <v>7</v>
@@ -17939,7 +17970,7 @@
         <v>7</v>
       </c>
       <c r="AH51" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI51" s="2">
         <v>0</v>
@@ -17966,13 +17997,13 @@
         <v>10</v>
       </c>
       <c r="AQ51" s="14" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AR51" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AS51" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AT51" s="2">
         <v>0</v>
@@ -18000,10 +18031,10 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>7</v>
@@ -18024,22 +18055,22 @@
         <v>2</v>
       </c>
       <c r="O52" s="2">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="P52" s="2">
         <v>0</v>
       </c>
       <c r="Q52" s="2">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="R52" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="S52" s="2">
         <v>0</v>
       </c>
       <c r="T52" s="2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U52" s="2">
         <v>0</v>
@@ -18060,13 +18091,13 @@
         <v>0</v>
       </c>
       <c r="AA52" s="2">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="AB52" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC52" s="3" t="s">
-        <v>7</v>
+        <v>179</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>7</v>
@@ -18096,7 +18127,7 @@
         <v>0</v>
       </c>
       <c r="AM52" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AN52" s="2">
         <v>0</v>
@@ -18108,13 +18139,13 @@
         <v>10</v>
       </c>
       <c r="AQ52" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AR52" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AS52" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AT52" s="2">
         <v>0</v>
@@ -18142,10 +18173,10 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>7</v>
@@ -18166,7 +18197,7 @@
         <v>2</v>
       </c>
       <c r="O53" s="2">
-        <v>480</v>
+        <v>1200</v>
       </c>
       <c r="P53" s="2">
         <v>0</v>
@@ -18175,13 +18206,13 @@
         <v>32</v>
       </c>
       <c r="R53" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S53" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T53" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U53" s="2">
         <v>0</v>
@@ -18202,11 +18233,11 @@
         <v>0</v>
       </c>
       <c r="AA53" s="2">
+        <v>130</v>
+      </c>
+      <c r="AB53" s="2">
         <v>50</v>
       </c>
-      <c r="AB53" s="2">
-        <v>0</v>
-      </c>
       <c r="AC53" s="3" t="s">
         <v>7</v>
       </c>
@@ -18238,7 +18269,7 @@
         <v>0</v>
       </c>
       <c r="AM53" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AN53" s="2">
         <v>0</v>
@@ -18250,13 +18281,13 @@
         <v>10</v>
       </c>
       <c r="AQ53" s="14" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="AR53" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AS53" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AT53" s="2">
         <v>0</v>
@@ -18284,13 +18315,13 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>294</v>
+        <v>7</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>7</v>
@@ -18308,22 +18339,22 @@
         <v>2</v>
       </c>
       <c r="O54" s="2">
-        <v>550</v>
+        <v>480</v>
       </c>
       <c r="P54" s="2">
         <v>0</v>
       </c>
       <c r="Q54" s="2">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="R54" s="2">
         <v>0</v>
       </c>
       <c r="S54" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T54" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U54" s="2">
         <v>0</v>
@@ -18392,13 +18423,13 @@
         <v>10</v>
       </c>
       <c r="AQ54" s="14" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="AR54" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AS54" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AT54" s="2">
         <v>0</v>
@@ -18426,13 +18457,13 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>7</v>
+        <v>294</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>7</v>
@@ -18450,25 +18481,25 @@
         <v>2</v>
       </c>
       <c r="O55" s="2">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="P55" s="2">
         <v>0</v>
       </c>
       <c r="Q55" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="R55" s="2">
         <v>0</v>
       </c>
       <c r="S55" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T55" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U55" s="2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="V55" s="2">
         <v>0</v>
@@ -18486,7 +18517,7 @@
         <v>0</v>
       </c>
       <c r="AA55" s="2">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="AB55" s="2">
         <v>0</v>
@@ -18522,7 +18553,7 @@
         <v>0</v>
       </c>
       <c r="AM55" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AN55" s="2">
         <v>0</v>
@@ -18534,13 +18565,13 @@
         <v>10</v>
       </c>
       <c r="AQ55" s="14" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="AR55" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AS55" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AT55" s="2">
         <v>0</v>
@@ -18568,10 +18599,10 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>7</v>
@@ -18592,25 +18623,25 @@
         <v>2</v>
       </c>
       <c r="O56" s="2">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="P56" s="2">
         <v>0</v>
       </c>
       <c r="Q56" s="2">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="R56" s="2">
         <v>0</v>
       </c>
       <c r="S56" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T56" s="2">
         <v>0</v>
       </c>
       <c r="U56" s="2">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="V56" s="2">
         <v>0</v>
@@ -18628,7 +18659,7 @@
         <v>0</v>
       </c>
       <c r="AA56" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AB56" s="2">
         <v>0</v>
@@ -18664,7 +18695,7 @@
         <v>0</v>
       </c>
       <c r="AM56" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AN56" s="2">
         <v>0</v>
@@ -18676,13 +18707,13 @@
         <v>10</v>
       </c>
       <c r="AQ56" s="14" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="AR56" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AS56" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AT56" s="2">
         <v>0</v>
@@ -18710,10 +18741,10 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>7</v>
@@ -18734,7 +18765,7 @@
         <v>2</v>
       </c>
       <c r="O57" s="2">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="P57" s="2">
         <v>0</v>
@@ -18818,13 +18849,13 @@
         <v>10</v>
       </c>
       <c r="AQ57" s="14" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AR57" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AS57" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AT57" s="2">
         <v>0</v>
@@ -18843,19 +18874,19 @@
         <v>0</v>
       </c>
       <c r="D58" s="2">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="E58" s="2">
-        <v>9999</v>
+        <v>20</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>7</v>
+        <v>175</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>7</v>
@@ -18864,7 +18895,7 @@
         <v>7</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="L58" s="2">
         <v>0</v>
@@ -18873,16 +18904,16 @@
         <v>1</v>
       </c>
       <c r="N58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" s="2">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="P58" s="2">
         <v>0</v>
       </c>
       <c r="Q58" s="2">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="R58" s="2">
         <v>0</v>
@@ -18891,10 +18922,10 @@
         <v>0</v>
       </c>
       <c r="T58" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="U58" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="V58" s="2">
         <v>0</v>
@@ -18912,7 +18943,7 @@
         <v>0</v>
       </c>
       <c r="AA58" s="2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AB58" s="2">
         <v>0</v>
@@ -18948,7 +18979,7 @@
         <v>0</v>
       </c>
       <c r="AM58" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AN58" s="2">
         <v>0</v>
@@ -18960,15 +18991,157 @@
         <v>10</v>
       </c>
       <c r="AQ58" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="AR58" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="AS58" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="AT58" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:46" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B59" s="2">
+        <f t="shared" si="1"/>
+        <v>10057</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0</v>
+      </c>
+      <c r="D59" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E59" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L59" s="2">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2">
+        <v>1</v>
+      </c>
+      <c r="N59" s="2">
+        <v>1</v>
+      </c>
+      <c r="O59" s="2">
+        <v>300</v>
+      </c>
+      <c r="P59" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>54</v>
+      </c>
+      <c r="R59" s="2">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
+        <v>0</v>
+      </c>
+      <c r="T59" s="2">
+        <v>80</v>
+      </c>
+      <c r="U59" s="2">
+        <v>0</v>
+      </c>
+      <c r="V59" s="2">
+        <v>0</v>
+      </c>
+      <c r="W59" s="2">
+        <v>0</v>
+      </c>
+      <c r="X59" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM59" s="2">
+        <v>5</v>
+      </c>
+      <c r="AN59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP59" s="2">
+        <v>10</v>
+      </c>
+      <c r="AQ59" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="AR58" s="5" t="s">
+      <c r="AR59" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="AS58" s="4" t="s">
+      <c r="AS59" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AT58" s="2">
+      <c r="AT59" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65218C8F-A3E6-4F32-9CA7-2E6A0BDF405A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F225B2-998E-459E-82F0-CB30E28C4E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="870" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3740" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3740" uniqueCount="306">
   <si>
     <t>desc</t>
   </si>
@@ -2593,6 +2593,31 @@
     </rPh>
     <rPh sb="46" eb="49">
       <t>ライヒンキャク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>あるご婦人の方から、パーティー用に紅茶がほしいそうよ。&lt;color=#FF78B4&gt;ラベンダーティー&lt;/color&gt;のような、少し香りが強めのものがいいみたい。</t>
+    <rPh sb="3" eb="5">
+      <t>フジン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コウチャ</t>
+    </rPh>
+    <rPh sb="63" eb="64">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>カオ</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ツヨ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -14737,7 +14762,7 @@
         <v>82</v>
       </c>
       <c r="AS28" s="4" t="s">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AT28" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C472333-8743-4FA5-9F91-7632B1FE259A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B194DFD-9881-4BC5-B7A1-690A944DDDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="1245" windowWidth="25560" windowHeight="14325" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="915" yWindow="300" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="309">
   <si>
     <t>desc</t>
   </si>
@@ -2637,6 +2637,10 @@
     <rPh sb="66" eb="67">
       <t>タ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>lumi_strawberry_cookie</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11120,11 +11124,11 @@
     </row>
     <row r="2" spans="1:47" s="10" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A2:A33" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="7">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" ref="B2:B33" si="1">(ROW()-2)+10000</f>
         <v>10000</v>
       </c>
       <c r="C2" s="7">
@@ -11265,11 +11269,11 @@
     </row>
     <row r="3" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10001</v>
       </c>
       <c r="C3" s="2">
@@ -11410,11 +11414,11 @@
     </row>
     <row r="4" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10002</v>
       </c>
       <c r="C4" s="2">
@@ -11555,11 +11559,11 @@
     </row>
     <row r="5" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10003</v>
       </c>
       <c r="C5" s="2">
@@ -11700,11 +11704,11 @@
     </row>
     <row r="6" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10004</v>
       </c>
       <c r="C6" s="2">
@@ -11845,11 +11849,11 @@
     </row>
     <row r="7" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10005</v>
       </c>
       <c r="C7" s="2">
@@ -11990,11 +11994,11 @@
     </row>
     <row r="8" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10006</v>
       </c>
       <c r="C8" s="2">
@@ -12135,11 +12139,11 @@
     </row>
     <row r="9" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10007</v>
       </c>
       <c r="C9" s="2">
@@ -12280,11 +12284,11 @@
     </row>
     <row r="10" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10008</v>
       </c>
       <c r="C10" s="2">
@@ -12425,11 +12429,11 @@
     </row>
     <row r="11" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10009</v>
       </c>
       <c r="C11" s="2">
@@ -12570,11 +12574,11 @@
     </row>
     <row r="12" spans="1:47" s="19" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B12" s="15">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10010</v>
       </c>
       <c r="C12" s="15">
@@ -12715,11 +12719,11 @@
     </row>
     <row r="13" spans="1:47" s="19" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="15">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="15">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10011</v>
       </c>
       <c r="C13" s="15">
@@ -12860,11 +12864,11 @@
     </row>
     <row r="14" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10012</v>
       </c>
       <c r="C14" s="2">
@@ -13005,11 +13009,11 @@
     </row>
     <row r="15" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10013</v>
       </c>
       <c r="C15" s="2">
@@ -13150,11 +13154,11 @@
     </row>
     <row r="16" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10014</v>
       </c>
       <c r="C16" s="2">
@@ -13295,11 +13299,11 @@
     </row>
     <row r="17" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10015</v>
       </c>
       <c r="C17" s="2">
@@ -13440,11 +13444,11 @@
     </row>
     <row r="18" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10016</v>
       </c>
       <c r="C18" s="2">
@@ -13585,11 +13589,11 @@
     </row>
     <row r="19" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10017</v>
       </c>
       <c r="C19" s="2">
@@ -13730,11 +13734,11 @@
     </row>
     <row r="20" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10018</v>
       </c>
       <c r="C20" s="2">
@@ -13875,11 +13879,11 @@
     </row>
     <row r="21" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10019</v>
       </c>
       <c r="C21" s="2">
@@ -14020,11 +14024,11 @@
     </row>
     <row r="22" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10020</v>
       </c>
       <c r="C22" s="2">
@@ -14165,11 +14169,11 @@
     </row>
     <row r="23" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10021</v>
       </c>
       <c r="C23" s="2">
@@ -14310,11 +14314,11 @@
     </row>
     <row r="24" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10022</v>
       </c>
       <c r="C24" s="2">
@@ -14455,11 +14459,11 @@
     </row>
     <row r="25" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10023</v>
       </c>
       <c r="C25" s="2">
@@ -14600,11 +14604,11 @@
     </row>
     <row r="26" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10024</v>
       </c>
       <c r="C26" s="2">
@@ -14745,11 +14749,11 @@
     </row>
     <row r="27" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10025</v>
       </c>
       <c r="C27" s="2">
@@ -14890,11 +14894,11 @@
     </row>
     <row r="28" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10026</v>
       </c>
       <c r="C28" s="2">
@@ -15035,11 +15039,11 @@
     </row>
     <row r="29" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10027</v>
       </c>
       <c r="C29" s="2">
@@ -15180,11 +15184,11 @@
     </row>
     <row r="30" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10028</v>
       </c>
       <c r="C30" s="2">
@@ -15325,11 +15329,11 @@
     </row>
     <row r="31" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10029</v>
       </c>
       <c r="C31" s="2">
@@ -15470,11 +15474,11 @@
     </row>
     <row r="32" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10030</v>
       </c>
       <c r="C32" s="2">
@@ -15615,11 +15619,11 @@
     </row>
     <row r="33" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="1"/>
         <v>10031</v>
       </c>
       <c r="C33" s="2">
@@ -15760,11 +15764,11 @@
     </row>
     <row r="34" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A34:A57" si="2">ROW()-2</f>
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" ref="B34:B57" si="3">(ROW()-2)+10000</f>
         <v>10032</v>
       </c>
       <c r="C34" s="2">
@@ -15905,11 +15909,11 @@
     </row>
     <row r="35" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10033</v>
       </c>
       <c r="C35" s="2">
@@ -16050,11 +16054,11 @@
     </row>
     <row r="36" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10034</v>
       </c>
       <c r="C36" s="2">
@@ -16076,7 +16080,7 @@
         <v>159</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>7</v>
+        <v>308</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>7</v>
@@ -16195,11 +16199,11 @@
     </row>
     <row r="37" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10035</v>
       </c>
       <c r="C37" s="2">
@@ -16340,11 +16344,11 @@
     </row>
     <row r="38" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10036</v>
       </c>
       <c r="C38" s="2">
@@ -16485,11 +16489,11 @@
     </row>
     <row r="39" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10037</v>
       </c>
       <c r="C39" s="2">
@@ -16630,11 +16634,11 @@
     </row>
     <row r="40" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10038</v>
       </c>
       <c r="C40" s="2">
@@ -16775,11 +16779,11 @@
     </row>
     <row r="41" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10039</v>
       </c>
       <c r="C41" s="2">
@@ -16920,11 +16924,11 @@
     </row>
     <row r="42" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10040</v>
       </c>
       <c r="C42" s="2">
@@ -17065,11 +17069,11 @@
     </row>
     <row r="43" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10041</v>
       </c>
       <c r="C43" s="2">
@@ -17210,11 +17214,11 @@
     </row>
     <row r="44" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10042</v>
       </c>
       <c r="C44" s="2">
@@ -17355,11 +17359,11 @@
     </row>
     <row r="45" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10043</v>
       </c>
       <c r="C45" s="2">
@@ -17500,11 +17504,11 @@
     </row>
     <row r="46" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10044</v>
       </c>
       <c r="C46" s="2">
@@ -17645,11 +17649,11 @@
     </row>
     <row r="47" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10045</v>
       </c>
       <c r="C47" s="2">
@@ -17790,11 +17794,11 @@
     </row>
     <row r="48" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10046</v>
       </c>
       <c r="C48" s="2">
@@ -17935,11 +17939,11 @@
     </row>
     <row r="49" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10047</v>
       </c>
       <c r="C49" s="2">
@@ -18080,11 +18084,11 @@
     </row>
     <row r="50" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10048</v>
       </c>
       <c r="C50" s="2">
@@ -18225,11 +18229,11 @@
     </row>
     <row r="51" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10049</v>
       </c>
       <c r="C51" s="2">
@@ -18370,11 +18374,11 @@
     </row>
     <row r="52" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10050</v>
       </c>
       <c r="C52" s="2">
@@ -18515,11 +18519,11 @@
     </row>
     <row r="53" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10051</v>
       </c>
       <c r="C53" s="2">
@@ -18660,11 +18664,11 @@
     </row>
     <row r="54" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10052</v>
       </c>
       <c r="C54" s="2">
@@ -18805,11 +18809,11 @@
     </row>
     <row r="55" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10053</v>
       </c>
       <c r="C55" s="2">
@@ -18950,11 +18954,11 @@
     </row>
     <row r="56" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10054</v>
       </c>
       <c r="C56" s="2">
@@ -19095,11 +19099,11 @@
     </row>
     <row r="57" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>55</v>
       </c>
       <c r="B57" s="2">
-        <f>(ROW()-2)+10000</f>
+        <f t="shared" si="3"/>
         <v>10055</v>
       </c>
       <c r="C57" s="2">

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B194DFD-9881-4BC5-B7A1-690A944DDDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA5F2AB-D88D-4958-A488-349C66375570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="915" yWindow="300" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1065" yWindow="1080" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -20168,7 +20168,7 @@
         <v>0</v>
       </c>
       <c r="AP3" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AQ3" s="14" t="s">
         <v>246</v>
@@ -20313,7 +20313,7 @@
         <v>0</v>
       </c>
       <c r="AP4" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AQ4" s="14" t="s">
         <v>257</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA5F2AB-D88D-4958-A488-349C66375570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4564B3-CC2C-4D59-9FA9-DF263A02A7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1065" yWindow="1080" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1005" yWindow="600" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="311">
   <si>
     <t>desc</t>
   </si>
@@ -2542,10 +2542,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>a_FrozenFruits</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>strawberry_sponge_cake</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2641,6 +2637,39 @@
   </si>
   <si>
     <t>lumi_strawberry_cookie</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ある貴族のお客様が、お茶会で食べるお菓子を探してるそうよ。&lt;color=#FF78B4&gt;ラスク&lt;/color&gt;があれば、喜ばれるかも..。</t>
+    <rPh sb="2" eb="4">
+      <t>キゾク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キャクサマ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>チャカイ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>サガ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>frozen_fruits</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>frozen_fruitsset</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3243,7 +3272,7 @@
         <v>245</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>32</v>
@@ -11110,7 +11139,7 @@
         <v>245</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>32</v>
@@ -14596,7 +14625,7 @@
         <v>130</v>
       </c>
       <c r="AT25" s="4" t="s">
-        <v>64</v>
+        <v>308</v>
       </c>
       <c r="AU25" s="2">
         <v>0</v>
@@ -14886,7 +14915,7 @@
         <v>82</v>
       </c>
       <c r="AT27" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AU27" s="2">
         <v>0</v>
@@ -16080,7 +16109,7 @@
         <v>159</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>7</v>
@@ -16219,10 +16248,10 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>7</v>
@@ -16333,10 +16362,10 @@
         <v>16</v>
       </c>
       <c r="AS37" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AT37" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="AT37" s="4" t="s">
-        <v>303</v>
       </c>
       <c r="AU37" s="2">
         <v>0</v>
@@ -16799,10 +16828,10 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>39</v>
+        <v>310</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>7</v>
+        <v>309</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>7</v>
@@ -16811,7 +16840,7 @@
         <v>7</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>300</v>
+        <v>7</v>
       </c>
       <c r="L41" s="2">
         <v>0</v>
@@ -17206,7 +17235,7 @@
         <v>187</v>
       </c>
       <c r="AT43" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AU43" s="2">
         <v>0</v>
@@ -17587,7 +17616,7 @@
         <v>50</v>
       </c>
       <c r="AB46" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AC46" s="3" t="s">
         <v>7</v>
@@ -18801,7 +18830,7 @@
         <v>198</v>
       </c>
       <c r="AT54" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AU54" s="2">
         <v>0</v>
@@ -19412,7 +19441,7 @@
         <v>245</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>32</v>
@@ -19884,7 +19913,7 @@
         <v>245</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>32</v>
@@ -20646,7 +20675,7 @@
         <v>245</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AS1" s="1" t="s">
         <v>32</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4564B3-CC2C-4D59-9FA9-DF263A02A7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4F72E3-7CB1-44F4-8468-D103DE10A261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1005" yWindow="600" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2565" yWindow="1275" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -20086,7 +20086,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
@@ -20231,7 +20231,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4F72E3-7CB1-44F4-8468-D103DE10A261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EFB50D-CFD6-48B4-B16F-02ED58DFF731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="1275" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1530" yWindow="1080" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -20131,7 +20131,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="U3" s="2">
         <v>0</v>
@@ -20155,7 +20155,7 @@
         <v>50</v>
       </c>
       <c r="AB3" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AC3" s="3" t="s">
         <v>7</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EFB50D-CFD6-48B4-B16F-02ED58DFF731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33535596-2A85-44CF-BEC8-CCD7B7A5201D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="1080" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="390" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="339">
   <si>
     <t>desc</t>
   </si>
@@ -2670,6 +2670,234 @@
   </si>
   <si>
     <t>frozen_fruitsset</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>apple_pie</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アップルパイが食べたい！</t>
+    <rPh sb="7" eb="8">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
+さくさくのアップルパイが欲しいそうだわ。</t>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Chocolate</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>chocolate_black</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレート製作のご依頼</t>
+    <rPh sb="6" eb="8">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>イライ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
+お店の看板になるチョコレートを希望してるわ。</t>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ミセ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>カンバン</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>chocolate_aquamarine</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>aquamarine_chocolate</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>遥かなる蒼が食べたい！</t>
+    <rPh sb="0" eb="1">
+      <t>ハル</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
+世にも珍しい青色のチョコレートを食べたいそうよ。</t>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>メズラ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>アオイロ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>opera</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>オペラを作ってほしい！</t>
+    <rPh sb="4" eb="5">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mont_blanc</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>モンブランがほしい！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
+秋らしい風味を感じるケーキを探してるみたい。</t>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>フウミ</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ショートケーキが食べたい！</t>
+    <rPh sb="8" eb="9">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
+かわいくてシンプルなケーキを味わいたいそうよ。</t>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>アジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>cheese_cake</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CheeseCake</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チーズケーキが食べたい！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
+しっとりしたチーズケーキを食べてみたいそうよ。</t>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>a_ChocolateTwister</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>chocolate_black_twister</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>chocolate_black_twister_3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風のチョコレートが食べたい！</t>
+    <rPh sb="0" eb="1">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
+カフェにぴったりのケーキを探してるみたい。</t>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
+不思議な風のチョコレートを食べたいそうよ。</t>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="43" eb="46">
+      <t>フシギ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>カゼ</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>タ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -19755,7 +19983,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU13"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
@@ -19927,11 +20155,11 @@
     </row>
     <row r="2" spans="1:47" s="10" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
-        <f t="shared" ref="A2:A5" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A13" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="7">
-        <f>(ROW()-2)+30000</f>
+        <f t="shared" ref="B2:B12" si="1">(ROW()-2)+30000</f>
         <v>30000</v>
       </c>
       <c r="C2" s="7">
@@ -20072,11 +20300,11 @@
     </row>
     <row r="3" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" ref="A3:A12" si="2">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <f>(ROW()-2)+30000</f>
+        <f t="shared" si="1"/>
         <v>30001</v>
       </c>
       <c r="C3" s="2">
@@ -20113,7 +20341,7 @@
         <v>1</v>
       </c>
       <c r="N3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" s="2">
         <v>850</v>
@@ -20217,11 +20445,11 @@
     </row>
     <row r="4" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <f>(ROW()-2)+30000</f>
+        <f t="shared" si="1"/>
         <v>30002</v>
       </c>
       <c r="C4" s="2">
@@ -20362,30 +20590,30 @@
     </row>
     <row r="5" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <f t="shared" ref="B5" si="1">(ROW()-2)+30000</f>
+        <f t="shared" si="1"/>
         <v>30003</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
       </c>
       <c r="D5" s="2">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>9999</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>7</v>
+        <v>300</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>7</v>
@@ -20394,7 +20622,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -20406,44 +20634,44 @@
         <v>1</v>
       </c>
       <c r="O5" s="2">
-        <v>300</v>
+        <v>2200</v>
       </c>
       <c r="P5" s="2">
         <v>0</v>
       </c>
       <c r="Q5" s="2">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="R5" s="2">
         <v>0</v>
       </c>
       <c r="S5" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T5" s="2">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2">
+        <v>90</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0</v>
+      </c>
+      <c r="W5" s="2">
+        <v>0</v>
+      </c>
+      <c r="X5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="2">
         <v>80</v>
       </c>
-      <c r="U5" s="2">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2">
-        <v>0</v>
-      </c>
-      <c r="X5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="2">
-        <v>50</v>
-      </c>
       <c r="AB5" s="2">
         <v>0</v>
       </c>
@@ -20478,30 +20706,1190 @@
         <v>0</v>
       </c>
       <c r="AM5" s="2">
-        <v>5</v>
-      </c>
-      <c r="AN5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="2">
+        <v>13</v>
+      </c>
+      <c r="AN5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="3">
         <v>0</v>
       </c>
       <c r="AP5" s="2">
         <v>30</v>
       </c>
       <c r="AQ5" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AR5" s="2">
+        <v>9</v>
+      </c>
+      <c r="AS5" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="AT5" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="AU5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <f t="shared" si="1"/>
+        <v>30004</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2">
+        <v>1700</v>
+      </c>
+      <c r="P6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>54</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2">
+        <v>83</v>
+      </c>
+      <c r="T6" s="2">
+        <v>90</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="2">
+        <v>8</v>
+      </c>
+      <c r="AN6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="2">
+        <v>30</v>
+      </c>
+      <c r="AQ6" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AR6" s="2">
+        <v>9</v>
+      </c>
+      <c r="AS6" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="AT6" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="AU6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <f t="shared" si="1"/>
+        <v>30005</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>15</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2">
+        <v>5000</v>
+      </c>
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>180</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <v>50</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <v>100</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="2">
+        <v>12</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="2">
+        <v>30</v>
+      </c>
+      <c r="AQ7" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AR7" s="2">
+        <v>9</v>
+      </c>
+      <c r="AS7" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="AT7" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="AU7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <f t="shared" si="1"/>
+        <v>30006</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>18</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>1</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2">
+        <v>6500</v>
+      </c>
+      <c r="P8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>180</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <v>40</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2">
+        <v>90</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="2">
+        <v>13</v>
+      </c>
+      <c r="AN8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="2">
+        <v>30</v>
+      </c>
+      <c r="AQ8" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AR8" s="2">
+        <v>9</v>
+      </c>
+      <c r="AS8" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="AT8" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="AU8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <f t="shared" si="1"/>
+        <v>30007</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>18</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="2">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2">
+        <v>1800</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>60</v>
+      </c>
+      <c r="R9" s="2">
+        <v>30</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
+        <v>130</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="2">
+        <v>13</v>
+      </c>
+      <c r="AN9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="2">
+        <v>30</v>
+      </c>
+      <c r="AQ9" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AR9" s="2">
+        <v>9</v>
+      </c>
+      <c r="AS9" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="AT9" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="AU9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <f t="shared" si="1"/>
+        <v>30008</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>15</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>1</v>
+      </c>
+      <c r="N10" s="2">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2">
+        <v>3200</v>
+      </c>
+      <c r="P10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>80</v>
+      </c>
+      <c r="R10" s="2">
+        <v>230</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2">
+        <v>70</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="2">
+        <v>10</v>
+      </c>
+      <c r="AN10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="2">
+        <v>30</v>
+      </c>
+      <c r="AQ10" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AR10" s="2">
+        <v>9</v>
+      </c>
+      <c r="AS10" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="AT10" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="AU10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <f t="shared" si="1"/>
+        <v>30009</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>1</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2">
+        <v>8500</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>80</v>
+      </c>
+      <c r="R11" s="2">
+        <v>230</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2">
+        <v>70</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="2">
+        <v>15</v>
+      </c>
+      <c r="AN11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="2">
+        <v>30</v>
+      </c>
+      <c r="AQ11" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AR11" s="2">
+        <v>9</v>
+      </c>
+      <c r="AS11" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="AT11" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="AU11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <f t="shared" si="1"/>
+        <v>30010</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>1</v>
+      </c>
+      <c r="N12" s="2">
+        <v>1</v>
+      </c>
+      <c r="O12" s="2">
+        <v>4500</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>80</v>
+      </c>
+      <c r="R12" s="2">
+        <v>230</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2">
+        <v>70</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="2">
+        <v>10</v>
+      </c>
+      <c r="AN12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="2">
+        <v>30</v>
+      </c>
+      <c r="AQ12" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="AR12" s="2">
+        <v>9</v>
+      </c>
+      <c r="AS12" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="AT12" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="AU12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <f t="shared" ref="B13" si="3">(ROW()-2)+30000</f>
+        <v>30011</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E13" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>1</v>
+      </c>
+      <c r="N13" s="2">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2">
+        <v>300</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>54</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2">
+        <v>80</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="2">
+        <v>5</v>
+      </c>
+      <c r="AN13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="2">
+        <v>30</v>
+      </c>
+      <c r="AQ13" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="AR5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="5" t="s">
+      <c r="AR13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="AT5" s="4" t="s">
+      <c r="AT13" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AU5" s="2">
+      <c r="AU13" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33535596-2A85-44CF-BEC8-CCD7B7A5201D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD44C2C-B3D7-45AC-AD00-D46D14CF0B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="390" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1485" yWindow="1155" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -14775,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="T25" s="2">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="U25" s="2">
         <v>0</v>
@@ -14920,7 +14920,7 @@
         <v>0</v>
       </c>
       <c r="T26" s="2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="U26" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD44C2C-B3D7-45AC-AD00-D46D14CF0B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E371A4B-5F48-49DD-A183-07BC1A87303F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="1155" windowWidth="25560" windowHeight="14325" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1995" yWindow="795" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="341">
   <si>
     <t>desc</t>
   </si>
@@ -2898,6 +2898,14 @@
     <rPh sb="56" eb="57">
       <t>タ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Lemon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CocoaPowder</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -15497,10 +15505,10 @@
         <v>0</v>
       </c>
       <c r="S30" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T30" s="2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U30" s="2">
         <v>0</v>
@@ -15527,10 +15535,10 @@
         <v>0</v>
       </c>
       <c r="AC30" s="3" t="s">
-        <v>7</v>
+        <v>339</v>
       </c>
       <c r="AD30" s="3" t="s">
-        <v>7</v>
+        <v>340</v>
       </c>
       <c r="AE30" s="3" t="s">
         <v>7</v>
@@ -15542,10 +15550,10 @@
         <v>7</v>
       </c>
       <c r="AH30" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI30" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AJ30" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E371A4B-5F48-49DD-A183-07BC1A87303F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEAAF4D-DC12-4B0C-BCA0-CEE333A03A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="795" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="1215" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="342">
   <si>
     <t>desc</t>
   </si>
@@ -2906,6 +2906,32 @@
   </si>
   <si>
     <t>CocoaPowder</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>井戸の近くに生えてる&lt;color=#FF78B4&gt;草&lt;/color&gt;があると助かるわね。
+採ってきてくれたらお駄賃をあげるわよ～。</t>
+    <rPh sb="0" eb="2">
+      <t>イド</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ハ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>タス</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ダチン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11961,7 +11987,7 @@
         <v>36</v>
       </c>
       <c r="AT5" s="4" t="s">
-        <v>38</v>
+        <v>341</v>
       </c>
       <c r="AU5" s="2">
         <v>0</v>
@@ -12735,7 +12761,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O11" s="2">
         <v>80</v>
@@ -16185,7 +16211,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="2">
-        <v>0</v>
+        <v>9999</v>
       </c>
       <c r="E35" s="2">
         <v>15</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEAAF4D-DC12-4B0C-BCA0-CEE333A03A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A178963-87D4-485A-96F2-B18A4FC4839E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="1215" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="1110" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="345">
   <si>
     <t>desc</t>
   </si>
@@ -2713,23 +2713,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
-お店の看板になるチョコレートを希望してるわ。</t>
-    <rPh sb="38" eb="40">
-      <t>イライ</t>
-    </rPh>
-    <rPh sb="44" eb="45">
-      <t>ミセ</t>
-    </rPh>
-    <rPh sb="46" eb="48">
-      <t>カンバン</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>キボウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>chocolate_aquamarine</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2751,26 +2734,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
-世にも珍しい青色のチョコレートを食べたいそうよ。</t>
-    <rPh sb="38" eb="40">
-      <t>イライ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>メズラ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>アオイロ</t>
-    </rPh>
-    <rPh sb="59" eb="60">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>opera</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2790,26 +2753,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
-秋らしい風味を感じるケーキを探してるみたい。</t>
-    <rPh sb="38" eb="40">
-      <t>イライ</t>
-    </rPh>
-    <rPh sb="43" eb="44">
-      <t>アキ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>フウミ</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>サガ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ショートケーキが食べたい！</t>
     <rPh sb="8" eb="9">
       <t>タ</t>
@@ -2817,17 +2760,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
-かわいくてシンプルなケーキを味わいたいそうよ。</t>
-    <rPh sb="38" eb="40">
-      <t>イライ</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>アジ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>cheese_cake</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2837,17 +2769,6 @@
   </si>
   <si>
     <t>チーズケーキが食べたい！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
-しっとりしたチーズケーキを食べてみたいそうよ。</t>
-    <rPh sb="38" eb="40">
-      <t>イライ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>タ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2868,34 +2789,6 @@
       <t>カゼ</t>
     </rPh>
     <rPh sb="9" eb="10">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
-カフェにぴったりのケーキを探してるみたい。</t>
-    <rPh sb="38" eb="40">
-      <t>イライ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
-      <t>サガ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
-不思議な風のチョコレートを食べたいそうよ。</t>
-    <rPh sb="38" eb="40">
-      <t>イライ</t>
-    </rPh>
-    <rPh sb="43" eb="46">
-      <t>フシギ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>カゼ</t>
-    </rPh>
-    <rPh sb="56" eb="57">
       <t>タ</t>
     </rPh>
     <phoneticPr fontId="2"/>
@@ -2931,6 +2824,161 @@
     </rPh>
     <rPh sb="55" eb="57">
       <t>ダチン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
+誕生日会で大きい派手なお菓子を飾りたいみたい。</t>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="43" eb="46">
+      <t>タンジョウビ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ハデ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>カザ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>東洋の貿易商</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;とある東洋の外国の方&lt;/color&gt;からのご依頼ね。
+世にも珍しい水色のチョコレートを売りたいみたい。</t>
+    <rPh sb="25" eb="27">
+      <t>ガイコク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>メズラ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>ミズイロ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>カフェ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;メイド学校の先生&lt;/color&gt;からのご依頼ね。
+しっとりしたチーズケーキを食べてみたいそうよ。</t>
+    <rPh sb="39" eb="41">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;オランジーナ百貨店&lt;/color&gt;からのご依頼ね。
+秋らしい風味を感じるケーキを探してるみたい。</t>
+    <rPh sb="25" eb="28">
+      <t>ヒャッカテン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>フウミ</t>
+    </rPh>
+    <rPh sb="52" eb="53">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>百貨店</t>
+    <rPh sb="0" eb="3">
+      <t>ヒャッカテン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;オランジーナ百貨店&lt;/color&gt;からのご依頼ね。
+高級なお土産用スイーツを探してるみたい。</t>
+    <rPh sb="40" eb="42">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>コウキュウ</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>ミヤゲヨウ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>サガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;ベリー好きの貴婦人&lt;/color&gt;からのご依頼ね。
+甘酸っぱいいちごをほおばって幸せを感じたいそうよ。</t>
+    <rPh sb="40" eb="42">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>アマズ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>シアワ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>カン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;裏通りのカフェ&lt;/color&gt;からのご依頼ね。
+お店の看板になるチョコレートを希望してるわ。</t>
+    <rPh sb="19" eb="21">
+      <t>ウラドオ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ミセ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>カンバン</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>キボウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -11987,7 +12035,7 @@
         <v>36</v>
       </c>
       <c r="AT5" s="4" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="AU5" s="2">
         <v>0</v>
@@ -15561,10 +15609,10 @@
         <v>0</v>
       </c>
       <c r="AC30" s="3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="AD30" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="AE30" s="3" t="s">
         <v>7</v>
@@ -20752,16 +20800,16 @@
         <v>30</v>
       </c>
       <c r="AQ5" s="14" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AR5" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AS5" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="AT5" s="4" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="AU5" s="3">
         <v>0</v>
@@ -20934,10 +20982,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>7</v>
@@ -21042,16 +21090,16 @@
         <v>30</v>
       </c>
       <c r="AQ7" s="14" t="s">
-        <v>257</v>
+        <v>341</v>
       </c>
       <c r="AR7" s="2">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AS7" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AT7" s="4" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AU7" s="3">
         <v>0</v>
@@ -21079,10 +21127,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>7</v>
@@ -21187,16 +21235,16 @@
         <v>30</v>
       </c>
       <c r="AQ8" s="14" t="s">
-        <v>257</v>
+        <v>341</v>
       </c>
       <c r="AR8" s="2">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AS8" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AT8" s="4" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="AU8" s="3">
         <v>0</v>
@@ -21224,7 +21272,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>7</v>
@@ -21236,7 +21284,7 @@
         <v>7</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -21332,16 +21380,16 @@
         <v>30</v>
       </c>
       <c r="AQ9" s="14" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AR9" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AS9" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="AT9" s="4" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="AU9" s="3">
         <v>0</v>
@@ -21477,16 +21525,16 @@
         <v>30</v>
       </c>
       <c r="AQ10" s="14" t="s">
-        <v>257</v>
+        <v>338</v>
       </c>
       <c r="AR10" s="2">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AS10" s="5" t="s">
         <v>316</v>
       </c>
       <c r="AT10" s="4" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="AU10" s="3">
         <v>0</v>
@@ -21514,10 +21562,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>7</v>
@@ -21622,16 +21670,16 @@
         <v>30</v>
       </c>
       <c r="AQ11" s="14" t="s">
-        <v>257</v>
+        <v>336</v>
       </c>
       <c r="AR11" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AS11" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AT11" s="4" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="AU11" s="3">
         <v>0</v>
@@ -21659,13 +21707,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>7</v>
@@ -21773,10 +21821,10 @@
         <v>9</v>
       </c>
       <c r="AS12" s="5" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="AT12" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AU12" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A178963-87D4-485A-96F2-B18A4FC4839E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070674E6-18F6-47DD-9013-DCB4045941D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="1110" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="349">
   <si>
     <t>desc</t>
   </si>
@@ -2703,16 +2703,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>チョコレート製作のご依頼</t>
-    <rPh sb="6" eb="8">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>イライ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>chocolate_aquamarine</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2735,13 +2725,6 @@
   </si>
   <si>
     <t>opera</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>オペラを作ってほしい！</t>
-    <rPh sb="4" eb="5">
-      <t>ツク</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2979,6 +2962,52 @@
     </rPh>
     <rPh sb="58" eb="60">
       <t>キボウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ご当地クッキーを作りたい！</t>
+    <rPh sb="1" eb="3">
+      <t>トウチ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;オランジーナ百貨店&lt;/color&gt;からのご依頼ね。
+観光客にウけるちょっと変わったクッキーがほしいみたい..。</t>
+    <rPh sb="45" eb="48">
+      <t>カンコウキャク</t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>lavender_cookie</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>neko_cookie_lavender</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>幻のオペラを作ってほしい！</t>
+    <rPh sb="0" eb="1">
+      <t>マボロシ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコレートを食べたい！</t>
+    <rPh sb="7" eb="8">
+      <t>タ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -12035,7 +12064,7 @@
         <v>36</v>
       </c>
       <c r="AT5" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AU5" s="2">
         <v>0</v>
@@ -13217,7 +13246,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -13362,7 +13391,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
@@ -13507,7 +13536,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="2">
         <v>0</v>
@@ -13652,7 +13681,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17" s="2">
         <v>0</v>
@@ -14377,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
@@ -14522,7 +14551,7 @@
         <v>9999</v>
       </c>
       <c r="E23" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
@@ -14667,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
@@ -14812,7 +14841,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
@@ -14957,7 +14986,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
@@ -15102,7 +15131,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F27" s="2">
         <v>0</v>
@@ -15247,7 +15276,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
@@ -15392,7 +15421,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
@@ -15537,7 +15566,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
@@ -15609,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="AC30" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AD30" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AE30" s="3" t="s">
         <v>7</v>
@@ -15676,13 +15705,13 @@
         <v>10029</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F31" s="2">
         <v>0</v>
@@ -15718,16 +15747,16 @@
         <v>0</v>
       </c>
       <c r="Q31" s="2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="R31" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S31" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T31" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="U31" s="2">
         <v>0</v>
@@ -15827,7 +15856,7 @@
         <v>9999</v>
       </c>
       <c r="E32" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
@@ -15972,7 +16001,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
@@ -16117,7 +16146,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
@@ -16262,7 +16291,7 @@
         <v>9999</v>
       </c>
       <c r="E35" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
@@ -16407,7 +16436,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
@@ -16552,7 +16581,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -16697,7 +16726,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F38" s="2">
         <v>0</v>
@@ -16842,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
@@ -16987,7 +17016,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
@@ -17126,13 +17155,13 @@
         <v>10039</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
@@ -17162,22 +17191,22 @@
         <v>4</v>
       </c>
       <c r="O41" s="2">
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="P41" s="2">
         <v>0</v>
       </c>
       <c r="Q41" s="2">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="R41" s="2">
         <v>0</v>
       </c>
       <c r="S41" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T41" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="U41" s="2">
         <v>0</v>
@@ -17277,7 +17306,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F42" s="2">
         <v>0</v>
@@ -17422,7 +17451,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -17567,7 +17596,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F44" s="2">
         <v>0</v>
@@ -17712,7 +17741,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
@@ -17857,7 +17886,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
@@ -18002,7 +18031,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F47" s="2">
         <v>0</v>
@@ -18147,7 +18176,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F48" s="2">
         <v>0</v>
@@ -18292,7 +18321,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
@@ -18437,7 +18466,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
@@ -18582,7 +18611,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F51" s="2">
         <v>0</v>
@@ -18727,7 +18756,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
@@ -18872,7 +18901,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F53" s="2">
         <v>0</v>
@@ -19017,7 +19046,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
@@ -20065,7 +20094,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AU13"/>
+  <dimension ref="A1:AU14"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
@@ -20237,11 +20266,11 @@
     </row>
     <row r="2" spans="1:47" s="10" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
-        <f t="shared" ref="A2:A13" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A14" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="7">
-        <f t="shared" ref="B2:B12" si="1">(ROW()-2)+30000</f>
+        <f t="shared" ref="B2:B13" si="1">(ROW()-2)+30000</f>
         <v>30000</v>
       </c>
       <c r="C2" s="7">
@@ -20382,7 +20411,7 @@
     </row>
     <row r="3" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A12" si="2">ROW()-2</f>
+        <f t="shared" ref="A3:A13" si="2">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="2">
@@ -20435,7 +20464,7 @@
         <v>27</v>
       </c>
       <c r="R3" s="2">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="S3" s="2">
         <v>0</v>
@@ -20716,7 +20745,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="2">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="P5" s="2">
         <v>0</v>
@@ -20806,10 +20835,10 @@
         <v>3</v>
       </c>
       <c r="AS5" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AT5" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AU5" s="3">
         <v>0</v>
@@ -20831,22 +20860,22 @@
         <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2">
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>7</v>
+        <v>291</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>7</v>
+        <v>290</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>7</v>
@@ -20861,22 +20890,22 @@
         <v>1</v>
       </c>
       <c r="O6" s="2">
-        <v>1700</v>
+        <v>1300</v>
       </c>
       <c r="P6" s="2">
         <v>0</v>
       </c>
       <c r="Q6" s="2">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="R6" s="2">
         <v>0</v>
       </c>
       <c r="S6" s="2">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="T6" s="2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="U6" s="2">
         <v>0</v>
@@ -20945,16 +20974,16 @@
         <v>30</v>
       </c>
       <c r="AQ6" s="14" t="s">
-        <v>257</v>
+        <v>339</v>
       </c>
       <c r="AR6" s="2">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AS6" s="5" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="AT6" s="4" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="AU6" s="3">
         <v>0</v>
@@ -20976,16 +21005,16 @@
         <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F7" s="2">
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>7</v>
@@ -21006,44 +21035,44 @@
         <v>1</v>
       </c>
       <c r="O7" s="2">
-        <v>5000</v>
+        <v>2100</v>
       </c>
       <c r="P7" s="2">
         <v>0</v>
       </c>
       <c r="Q7" s="2">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="R7" s="2">
         <v>0</v>
       </c>
       <c r="S7" s="2">
+        <v>83</v>
+      </c>
+      <c r="T7" s="2">
+        <v>90</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2">
         <v>50</v>
       </c>
-      <c r="T7" s="2">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2">
-        <v>100</v>
-      </c>
-      <c r="V7" s="2">
-        <v>0</v>
-      </c>
-      <c r="W7" s="2">
-        <v>0</v>
-      </c>
-      <c r="X7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>80</v>
-      </c>
       <c r="AB7" s="2">
         <v>0</v>
       </c>
@@ -21078,7 +21107,7 @@
         <v>0</v>
       </c>
       <c r="AM7" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AN7" s="3">
         <v>0</v>
@@ -21090,16 +21119,16 @@
         <v>30</v>
       </c>
       <c r="AQ7" s="14" t="s">
-        <v>341</v>
+        <v>257</v>
       </c>
       <c r="AR7" s="2">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AS7" s="5" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AT7" s="4" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="AU7" s="3">
         <v>0</v>
@@ -21121,16 +21150,16 @@
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>7</v>
@@ -21151,7 +21180,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="2">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="P8" s="2">
         <v>0</v>
@@ -21163,13 +21192,13 @@
         <v>0</v>
       </c>
       <c r="S8" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T8" s="2">
         <v>0</v>
       </c>
       <c r="U8" s="2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="V8" s="2">
         <v>0</v>
@@ -21223,7 +21252,7 @@
         <v>0</v>
       </c>
       <c r="AM8" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN8" s="3">
         <v>0</v>
@@ -21235,13 +21264,13 @@
         <v>30</v>
       </c>
       <c r="AQ8" s="14" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AR8" s="2">
         <v>23</v>
       </c>
       <c r="AS8" s="5" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="AT8" s="4" t="s">
         <v>340</v>
@@ -21266,13 +21295,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>7</v>
@@ -21284,7 +21313,7 @@
         <v>7</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -21296,16 +21325,16 @@
         <v>1</v>
       </c>
       <c r="O9" s="2">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="P9" s="2">
         <v>0</v>
       </c>
       <c r="Q9" s="2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="R9" s="2">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="S9" s="2">
         <v>0</v>
@@ -21314,10 +21343,10 @@
         <v>0</v>
       </c>
       <c r="U9" s="2">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="W9" s="2">
         <v>0</v>
@@ -21332,7 +21361,7 @@
         <v>0</v>
       </c>
       <c r="AA9" s="2">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AB9" s="2">
         <v>0</v>
@@ -21368,7 +21397,7 @@
         <v>0</v>
       </c>
       <c r="AM9" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AN9" s="3">
         <v>0</v>
@@ -21380,16 +21409,16 @@
         <v>30</v>
       </c>
       <c r="AQ9" s="14" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="AR9" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AS9" s="5" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="AT9" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AU9" s="3">
         <v>0</v>
@@ -21417,19 +21446,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>7</v>
+        <v>327</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>7</v>
+        <v>326</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>314</v>
+        <v>7</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
@@ -21441,7 +21470,7 @@
         <v>1</v>
       </c>
       <c r="O10" s="2">
-        <v>3200</v>
+        <v>4500</v>
       </c>
       <c r="P10" s="2">
         <v>0</v>
@@ -21450,7 +21479,7 @@
         <v>80</v>
       </c>
       <c r="R10" s="2">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="S10" s="2">
         <v>0</v>
@@ -21462,7 +21491,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="2">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="W10" s="2">
         <v>0</v>
@@ -21525,16 +21554,16 @@
         <v>30</v>
       </c>
       <c r="AQ10" s="14" t="s">
-        <v>338</v>
+        <v>257</v>
       </c>
       <c r="AR10" s="2">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AS10" s="5" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="AT10" s="4" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="AU10" s="3">
         <v>0</v>
@@ -21556,16 +21585,16 @@
         <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>7</v>
@@ -21586,44 +21615,44 @@
         <v>1</v>
       </c>
       <c r="O11" s="2">
-        <v>8500</v>
+        <v>6500</v>
       </c>
       <c r="P11" s="2">
         <v>0</v>
       </c>
       <c r="Q11" s="2">
+        <v>180</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>40</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>90</v>
+      </c>
+      <c r="V11" s="2">
+        <v>0</v>
+      </c>
+      <c r="W11" s="2">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2">
         <v>80</v>
       </c>
-      <c r="R11" s="2">
-        <v>230</v>
-      </c>
-      <c r="S11" s="2">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2">
-        <v>70</v>
-      </c>
-      <c r="W11" s="2">
-        <v>0</v>
-      </c>
-      <c r="X11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="2">
-        <v>50</v>
-      </c>
       <c r="AB11" s="2">
         <v>0</v>
       </c>
@@ -21658,7 +21687,7 @@
         <v>0</v>
       </c>
       <c r="AM11" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AN11" s="3">
         <v>0</v>
@@ -21670,16 +21699,16 @@
         <v>30</v>
       </c>
       <c r="AQ11" s="14" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AR11" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AS11" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AT11" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AU11" s="3">
         <v>0</v>
@@ -21701,25 +21730,25 @@
         <v>0</v>
       </c>
       <c r="E12" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>329</v>
+        <v>7</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>328</v>
+        <v>7</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>7</v>
+        <v>324</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
@@ -21731,44 +21760,44 @@
         <v>1</v>
       </c>
       <c r="O12" s="2">
-        <v>4500</v>
+        <v>1800</v>
       </c>
       <c r="P12" s="2">
         <v>0</v>
       </c>
       <c r="Q12" s="2">
+        <v>60</v>
+      </c>
+      <c r="R12" s="2">
+        <v>30</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
+        <v>130</v>
+      </c>
+      <c r="V12" s="2">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0</v>
+      </c>
+      <c r="X12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="2">
         <v>80</v>
       </c>
-      <c r="R12" s="2">
-        <v>230</v>
-      </c>
-      <c r="S12" s="2">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2">
-        <v>0</v>
-      </c>
-      <c r="U12" s="2">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2">
-        <v>70</v>
-      </c>
-      <c r="W12" s="2">
-        <v>0</v>
-      </c>
-      <c r="X12" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="2">
-        <v>50</v>
-      </c>
       <c r="AB12" s="2">
         <v>0</v>
       </c>
@@ -21803,7 +21832,7 @@
         <v>0</v>
       </c>
       <c r="AM12" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AN12" s="3">
         <v>0</v>
@@ -21815,16 +21844,16 @@
         <v>30</v>
       </c>
       <c r="AQ12" s="14" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AR12" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AS12" s="5" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="AT12" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AU12" s="3">
         <v>0</v>
@@ -21832,30 +21861,30 @@
     </row>
     <row r="13" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <f t="shared" ref="B13" si="3">(ROW()-2)+30000</f>
+        <f t="shared" si="1"/>
         <v>30011</v>
       </c>
       <c r="C13" s="2">
         <v>0</v>
       </c>
       <c r="D13" s="2">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2">
-        <v>9999</v>
+        <v>20</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>7</v>
+        <v>317</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>7</v>
@@ -21864,7 +21893,7 @@
         <v>7</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
@@ -21876,28 +21905,28 @@
         <v>1</v>
       </c>
       <c r="O13" s="2">
-        <v>300</v>
+        <v>7500</v>
       </c>
       <c r="P13" s="2">
         <v>0</v>
       </c>
       <c r="Q13" s="2">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="R13" s="2">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="S13" s="2">
         <v>0</v>
       </c>
       <c r="T13" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="U13" s="2">
         <v>0</v>
       </c>
       <c r="V13" s="2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="W13" s="2">
         <v>0</v>
@@ -21948,30 +21977,175 @@
         <v>0</v>
       </c>
       <c r="AM13" s="2">
-        <v>5</v>
-      </c>
-      <c r="AN13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="2">
+        <v>15</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
         <v>0</v>
       </c>
       <c r="AP13" s="2">
         <v>30</v>
       </c>
       <c r="AQ13" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="AR13" s="2">
+        <v>18</v>
+      </c>
+      <c r="AS13" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="AT13" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="AU13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:47" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <f t="shared" ref="B14" si="3">(ROW()-2)+30000</f>
+        <v>30012</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E14" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>1</v>
+      </c>
+      <c r="N14" s="2">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2">
+        <v>300</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>54</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2">
+        <v>80</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="2">
+        <v>5</v>
+      </c>
+      <c r="AN14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="2">
+        <v>30</v>
+      </c>
+      <c r="AQ14" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="AR13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="5" t="s">
+      <c r="AR14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="AT13" s="4" t="s">
+      <c r="AT14" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AU13" s="2">
+      <c r="AU14" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070674E6-18F6-47DD-9013-DCB4045941D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EE4E92-2517-420A-B0F8-4A3FDC29E82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2715" yWindow="600" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="351">
   <si>
     <t>desc</t>
   </si>
@@ -3009,6 +3009,14 @@
     <rPh sb="7" eb="8">
       <t>タ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>murasaki_mushroom_cookie</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Murasakinoko</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -20872,10 +20880,10 @@
         <v>345</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>291</v>
+        <v>58</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>290</v>
+        <v>349</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>7</v>
@@ -20932,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AC6" s="3" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="AD6" s="3" t="s">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="AE6" s="3" t="s">
         <v>7</v>
@@ -20947,10 +20955,10 @@
         <v>7</v>
       </c>
       <c r="AH6" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI6" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ6" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDB5246-78FE-4023-A9EB-88E6772E9324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4685011-6A2B-4FE9-A1D3-0164CE30B7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="1215" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1155" yWindow="1050" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -23066,7 +23066,7 @@
         <v>1</v>
       </c>
       <c r="T8" s="2">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="U8" s="2">
         <v>0</v>
@@ -23546,7 +23546,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="2">
-        <v>6500</v>
+        <v>16000</v>
       </c>
       <c r="U11" s="2">
         <v>0</v>
@@ -23706,7 +23706,7 @@
         <v>1</v>
       </c>
       <c r="T12" s="2">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="U12" s="2">
         <v>0</v>
@@ -23866,7 +23866,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="2">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="U13" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DFF805-1AFE-40E9-8E61-8452F984EBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D6CA2D-2A4D-4B32-AF68-8F5E692C5E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="1095" windowWidth="25560" windowHeight="14355" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2370" yWindow="1005" windowWidth="25485" windowHeight="14370" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -12775,7 +12775,7 @@
         <v>1</v>
       </c>
       <c r="U3" s="2">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="V3" s="2">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>1</v>
       </c>
       <c r="U13" s="15">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="V13" s="15">
         <v>0</v>
@@ -16524,7 +16524,7 @@
         <v>1</v>
       </c>
       <c r="U26" s="2">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="V26" s="2">
         <v>0</v>
@@ -17176,7 +17176,7 @@
         <v>1</v>
       </c>
       <c r="U30" s="21">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="V30" s="21">
         <v>0</v>
@@ -18154,7 +18154,7 @@
         <v>2</v>
       </c>
       <c r="U36" s="2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V36" s="2">
         <v>0</v>
@@ -19295,7 +19295,7 @@
         <v>2</v>
       </c>
       <c r="U43" s="2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V43" s="2">
         <v>0</v>
@@ -20110,7 +20110,7 @@
         <v>2</v>
       </c>
       <c r="U48" s="2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="V48" s="2">
         <v>0</v>
@@ -20273,7 +20273,7 @@
         <v>2</v>
       </c>
       <c r="U49" s="2">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="V49" s="2">
         <v>0</v>
@@ -20436,7 +20436,7 @@
         <v>2</v>
       </c>
       <c r="U50" s="2">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="V50" s="2">
         <v>0</v>
@@ -20762,7 +20762,7 @@
         <v>2</v>
       </c>
       <c r="U52" s="2">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="V52" s="2">
         <v>0</v>
@@ -22639,7 +22639,7 @@
         <v>1</v>
       </c>
       <c r="U3" s="2">
-        <v>850</v>
+        <v>650</v>
       </c>
       <c r="V3" s="2">
         <v>0</v>
@@ -22802,7 +22802,7 @@
         <v>1</v>
       </c>
       <c r="U4" s="2">
-        <v>6000</v>
+        <v>2200</v>
       </c>
       <c r="V4" s="2">
         <v>0</v>
@@ -22965,13 +22965,13 @@
         <v>1</v>
       </c>
       <c r="U5" s="2">
-        <v>2500</v>
+        <v>1700</v>
       </c>
       <c r="V5" s="2">
         <v>0</v>
       </c>
       <c r="W5" s="2">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="X5" s="2">
         <v>0</v>
@@ -22983,7 +22983,7 @@
         <v>0</v>
       </c>
       <c r="AA5" s="2">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AB5" s="2">
         <v>0</v>
@@ -23617,7 +23617,7 @@
         <v>1</v>
       </c>
       <c r="U9" s="21">
-        <v>3200</v>
+        <v>1300</v>
       </c>
       <c r="V9" s="21">
         <v>0</v>
@@ -23943,7 +23943,7 @@
         <v>1</v>
       </c>
       <c r="U11" s="2">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="V11" s="2">
         <v>0</v>
@@ -24106,7 +24106,7 @@
         <v>1</v>
       </c>
       <c r="U12" s="2">
-        <v>3000</v>
+        <v>2300</v>
       </c>
       <c r="V12" s="2">
         <v>0</v>
@@ -24269,7 +24269,7 @@
         <v>1</v>
       </c>
       <c r="U13" s="2">
-        <v>15000</v>
+        <v>2500</v>
       </c>
       <c r="V13" s="2">
         <v>0</v>
@@ -24290,7 +24290,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="2">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AC13" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6800D0CC-E53F-48FD-8BA4-9F12BA70188A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16B17E0-054D-4124-8E9D-1C44990B457B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1395" windowWidth="25485" windowHeight="14370" tabRatio="822" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1230" windowWidth="25485" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -17212,10 +17212,10 @@
         <v>0</v>
       </c>
       <c r="Y27" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z27" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA27" s="2">
         <v>0</v>
@@ -20432,7 +20432,7 @@
         <v>0</v>
       </c>
       <c r="AB46" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC46" s="2">
         <v>0</v>
@@ -20456,7 +20456,7 @@
         <v>50</v>
       </c>
       <c r="AJ46" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AK46" s="3" t="s">
         <v>7</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16B17E0-054D-4124-8E9D-1C44990B457B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C39F75-CA62-4F21-BA3E-9A63C334176A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1230" windowWidth="25485" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2445" yWindow="885" windowWidth="25485" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="367">
   <si>
     <t>desc</t>
   </si>
@@ -3086,6 +3086,37 @@
   </si>
   <si>
     <t>GirlSetScore</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>water_soda</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>炭酸水がほしい。</t>
+    <rPh sb="0" eb="3">
+      <t>タンサンスイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お酒のソーダ割のために、&lt;color=#FF78B4&gt;炭酸水&lt;/color&gt;がほしいのよ。
+もし持ってたら、持ってきてくれないかしら？</t>
+    <rPh sb="1" eb="2">
+      <t>サケ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ワリ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>タンサンスイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>モ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>モ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3192,7 +3223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3228,6 +3259,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -12712,7 +12751,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BC57"/>
+  <dimension ref="A1:BC58"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
@@ -18321,11 +18360,11 @@
     </row>
     <row r="34" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <f t="shared" ref="A34:A57" si="2">ROW()-2</f>
+        <f t="shared" ref="A34:A58" si="2">ROW()-2</f>
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <f t="shared" ref="B34:B57" si="3">(ROW()-2)+10000</f>
+        <f t="shared" ref="B34:B58" si="3">(ROW()-2)+10000</f>
         <v>10032</v>
       </c>
       <c r="C34" s="2">
@@ -19671,172 +19710,172 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="2">
+    <row r="42" spans="1:55" s="32" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="27">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="27">
         <f t="shared" si="3"/>
         <v>10040</v>
       </c>
-      <c r="C42" s="2">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2">
+      <c r="C42" s="27">
+        <v>1</v>
+      </c>
+      <c r="D42" s="27">
+        <v>0</v>
+      </c>
+      <c r="E42" s="27">
         <v>15</v>
       </c>
-      <c r="F42" s="2">
-        <v>0</v>
-      </c>
-      <c r="G42" s="2">
-        <v>0</v>
-      </c>
-      <c r="H42" s="2">
-        <v>0</v>
-      </c>
-      <c r="I42" s="2">
-        <v>0</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S42" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="T42" s="2">
-        <v>0</v>
-      </c>
-      <c r="U42" s="2">
+      <c r="F42" s="27">
+        <v>0</v>
+      </c>
+      <c r="G42" s="27">
+        <v>0</v>
+      </c>
+      <c r="H42" s="27">
+        <v>0</v>
+      </c>
+      <c r="I42" s="27">
+        <v>0</v>
+      </c>
+      <c r="J42" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="K42" s="27" t="s">
+        <v>364</v>
+      </c>
+      <c r="L42" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="M42" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="N42" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="O42" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="P42" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q42" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="R42" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="S42" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="T42" s="27">
+        <v>0</v>
+      </c>
+      <c r="U42" s="27">
         <v>1</v>
       </c>
-      <c r="V42" s="2">
-        <v>2</v>
-      </c>
-      <c r="W42" s="2">
-        <v>1500</v>
-      </c>
-      <c r="X42" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU42" s="2">
-        <v>8</v>
-      </c>
-      <c r="AV42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW42" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX42" s="2">
+      <c r="V42" s="27">
+        <v>4</v>
+      </c>
+      <c r="W42" s="27">
+        <v>450</v>
+      </c>
+      <c r="X42" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="27">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="27">
+        <v>50</v>
+      </c>
+      <c r="AJ42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL42" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM42" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN42" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO42" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AR42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AS42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AT42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AU42" s="27">
+        <v>3</v>
+      </c>
+      <c r="AV42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AW42" s="27">
+        <v>0</v>
+      </c>
+      <c r="AX42" s="27">
         <v>10</v>
       </c>
-      <c r="AY42" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="AZ42" s="2">
-        <v>5</v>
-      </c>
-      <c r="BA42" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="BB42" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="BC42" s="2">
+      <c r="AY42" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="AZ42" s="27">
+        <v>100</v>
+      </c>
+      <c r="BA42" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="BB42" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="BC42" s="27">
         <v>0</v>
       </c>
     </row>
@@ -19871,13 +19910,13 @@
         <v>0</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>223</v>
+        <v>163</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>176</v>
+        <v>7</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>297</v>
+        <v>7</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>7</v>
@@ -19898,7 +19937,7 @@
         <v>7</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="T43" s="2">
         <v>0</v>
@@ -19910,44 +19949,44 @@
         <v>2</v>
       </c>
       <c r="W43" s="2">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="X43" s="2">
         <v>0</v>
       </c>
       <c r="Y43" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="2">
         <v>80</v>
       </c>
-      <c r="Z43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="2">
+      <c r="AD43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="2">
         <v>80</v>
       </c>
-      <c r="AC43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI43" s="2">
-        <v>50</v>
-      </c>
       <c r="AJ43" s="2">
         <v>0</v>
       </c>
@@ -19982,7 +20021,7 @@
         <v>0</v>
       </c>
       <c r="AU43" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AV43" s="2">
         <v>0</v>
@@ -19994,16 +20033,16 @@
         <v>10</v>
       </c>
       <c r="AY43" s="14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AZ43" s="2">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="BA43" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BB43" s="4" t="s">
-        <v>305</v>
+        <v>204</v>
       </c>
       <c r="BC43" s="2">
         <v>0</v>
@@ -20040,16 +20079,16 @@
         <v>0</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>295</v>
+        <v>7</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>7</v>
@@ -20079,13 +20118,13 @@
         <v>2</v>
       </c>
       <c r="W44" s="2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X44" s="2">
         <v>0</v>
       </c>
       <c r="Y44" s="2">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="Z44" s="2">
         <v>0</v>
@@ -20094,7 +20133,7 @@
         <v>0</v>
       </c>
       <c r="AB44" s="2">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AC44" s="2">
         <v>0</v>
@@ -20112,11 +20151,11 @@
         <v>0</v>
       </c>
       <c r="AH44" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="2">
         <v>50</v>
       </c>
-      <c r="AI44" s="2">
-        <v>70</v>
-      </c>
       <c r="AJ44" s="2">
         <v>0</v>
       </c>
@@ -20151,7 +20190,7 @@
         <v>0</v>
       </c>
       <c r="AU44" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV44" s="2">
         <v>0</v>
@@ -20163,16 +20202,16 @@
         <v>10</v>
       </c>
       <c r="AY44" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AZ44" s="2">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="BA44" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BB44" s="4" t="s">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="BC44" s="2">
         <v>0</v>
@@ -20209,16 +20248,16 @@
         <v>0</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>7</v>
+        <v>295</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>7</v>
@@ -20248,7 +20287,7 @@
         <v>2</v>
       </c>
       <c r="W45" s="2">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="X45" s="2">
         <v>0</v>
@@ -20281,7 +20320,7 @@
         <v>0</v>
       </c>
       <c r="AH45" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AI45" s="2">
         <v>70</v>
@@ -20338,10 +20377,10 @@
         <v>16</v>
       </c>
       <c r="BA45" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BB45" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BC45" s="2">
         <v>0</v>
@@ -20378,13 +20417,13 @@
         <v>0</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>7</v>
+        <v>296</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>7</v>
@@ -20417,16 +20456,16 @@
         <v>2</v>
       </c>
       <c r="W46" s="2">
-        <v>850</v>
+        <v>600</v>
       </c>
       <c r="X46" s="2">
         <v>0</v>
       </c>
       <c r="Y46" s="2">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="Z46" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="2">
         <v>0</v>
@@ -20450,13 +20489,13 @@
         <v>0</v>
       </c>
       <c r="AH46" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI46" s="2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AJ46" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AK46" s="3" t="s">
         <v>7</v>
@@ -20501,16 +20540,16 @@
         <v>10</v>
       </c>
       <c r="AY46" s="14" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AZ46" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA46" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BB46" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BC46" s="2">
         <v>0</v>
@@ -20547,10 +20586,10 @@
         <v>0</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>7</v>
@@ -20586,47 +20625,47 @@
         <v>2</v>
       </c>
       <c r="W47" s="2">
-        <v>3500</v>
+        <v>850</v>
       </c>
       <c r="X47" s="2">
         <v>0</v>
       </c>
       <c r="Y47" s="2">
-        <v>330</v>
+        <v>32</v>
       </c>
       <c r="Z47" s="2">
+        <v>30</v>
+      </c>
+      <c r="AA47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="2">
+        <v>50</v>
+      </c>
+      <c r="AJ47" s="2">
         <v>40</v>
       </c>
-      <c r="AA47" s="2">
-        <v>110</v>
-      </c>
-      <c r="AB47" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="2">
-        <v>60</v>
-      </c>
-      <c r="AD47" s="2">
-        <v>90</v>
-      </c>
-      <c r="AE47" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI47" s="2">
-        <v>110</v>
-      </c>
-      <c r="AJ47" s="2">
-        <v>0</v>
-      </c>
       <c r="AK47" s="3" t="s">
         <v>7</v>
       </c>
@@ -20658,7 +20697,7 @@
         <v>0</v>
       </c>
       <c r="AU47" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AV47" s="2">
         <v>0</v>
@@ -20670,16 +20709,16 @@
         <v>10</v>
       </c>
       <c r="AY47" s="14" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="AZ47" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="BA47" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="BB47" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BC47" s="2">
         <v>0</v>
@@ -20716,10 +20755,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>7</v>
@@ -20755,28 +20794,28 @@
         <v>2</v>
       </c>
       <c r="W48" s="2">
-        <v>400</v>
+        <v>3500</v>
       </c>
       <c r="X48" s="2">
         <v>0</v>
       </c>
       <c r="Y48" s="2">
-        <v>32</v>
+        <v>330</v>
       </c>
       <c r="Z48" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA48" s="2">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB48" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="2">
         <v>60</v>
       </c>
-      <c r="AC48" s="2">
-        <v>20</v>
-      </c>
       <c r="AD48" s="2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AE48" s="2">
         <v>0</v>
@@ -20791,7 +20830,7 @@
         <v>0</v>
       </c>
       <c r="AI48" s="2">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AJ48" s="2">
         <v>0</v>
@@ -20827,7 +20866,7 @@
         <v>0</v>
       </c>
       <c r="AU48" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="AV48" s="2">
         <v>0</v>
@@ -20839,16 +20878,16 @@
         <v>10</v>
       </c>
       <c r="AY48" s="14" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="AZ48" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="BA48" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BB48" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="BC48" s="2">
         <v>0</v>
@@ -20885,10 +20924,10 @@
         <v>0</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>7</v>
@@ -20924,13 +20963,13 @@
         <v>2</v>
       </c>
       <c r="W49" s="2">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="X49" s="2">
         <v>0</v>
       </c>
       <c r="Y49" s="2">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="Z49" s="2">
         <v>0</v>
@@ -20939,10 +20978,10 @@
         <v>0</v>
       </c>
       <c r="AB49" s="2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AC49" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD49" s="2">
         <v>0</v>
@@ -20966,7 +21005,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="s">
-        <v>178</v>
+        <v>7</v>
       </c>
       <c r="AL49" s="3" t="s">
         <v>7</v>
@@ -20981,7 +21020,7 @@
         <v>7</v>
       </c>
       <c r="AP49" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AQ49" s="2">
         <v>0</v>
@@ -21008,16 +21047,16 @@
         <v>10</v>
       </c>
       <c r="AY49" s="14" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AZ49" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA49" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BB49" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BC49" s="2">
         <v>0</v>
@@ -21054,10 +21093,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>7</v>
@@ -21093,7 +21132,7 @@
         <v>2</v>
       </c>
       <c r="W50" s="2">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="X50" s="2">
         <v>0</v>
@@ -21135,7 +21174,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AL50" s="3" t="s">
         <v>7</v>
@@ -21150,7 +21189,7 @@
         <v>7</v>
       </c>
       <c r="AP50" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AQ50" s="2">
         <v>0</v>
@@ -21177,16 +21216,16 @@
         <v>10</v>
       </c>
       <c r="AY50" s="14" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AZ50" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA50" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BB50" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BC50" s="2">
         <v>0</v>
@@ -21223,10 +21262,10 @@
         <v>0</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>7</v>
@@ -21262,22 +21301,22 @@
         <v>2</v>
       </c>
       <c r="W51" s="2">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="X51" s="2">
         <v>0</v>
       </c>
       <c r="Y51" s="2">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="Z51" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AA51" s="2">
         <v>0</v>
       </c>
       <c r="AB51" s="2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AC51" s="2">
         <v>0</v>
@@ -21298,13 +21337,13 @@
         <v>0</v>
       </c>
       <c r="AI51" s="2">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="AJ51" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AK51" s="3" t="s">
-        <v>7</v>
+        <v>179</v>
       </c>
       <c r="AL51" s="3" t="s">
         <v>7</v>
@@ -21334,7 +21373,7 @@
         <v>0</v>
       </c>
       <c r="AU51" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AV51" s="2">
         <v>0</v>
@@ -21346,16 +21385,16 @@
         <v>10</v>
       </c>
       <c r="AY51" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AZ51" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA51" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BB51" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="BC51" s="2">
         <v>0</v>
@@ -21392,10 +21431,10 @@
         <v>0</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>7</v>
@@ -21431,7 +21470,7 @@
         <v>2</v>
       </c>
       <c r="W52" s="2">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="X52" s="2">
         <v>0</v>
@@ -21440,13 +21479,13 @@
         <v>32</v>
       </c>
       <c r="Z52" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA52" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AB52" s="2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AC52" s="2">
         <v>0</v>
@@ -21467,11 +21506,11 @@
         <v>0</v>
       </c>
       <c r="AI52" s="2">
+        <v>130</v>
+      </c>
+      <c r="AJ52" s="2">
         <v>50</v>
       </c>
-      <c r="AJ52" s="2">
-        <v>0</v>
-      </c>
       <c r="AK52" s="3" t="s">
         <v>7</v>
       </c>
@@ -21503,7 +21542,7 @@
         <v>0</v>
       </c>
       <c r="AU52" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AV52" s="2">
         <v>0</v>
@@ -21515,16 +21554,16 @@
         <v>10</v>
       </c>
       <c r="AY52" s="14" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="AZ52" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BA52" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BB52" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="BC52" s="2">
         <v>0</v>
@@ -21561,13 +21600,13 @@
         <v>0</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>293</v>
+        <v>7</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>7</v>
@@ -21600,22 +21639,22 @@
         <v>2</v>
       </c>
       <c r="W53" s="2">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="X53" s="2">
         <v>0</v>
       </c>
       <c r="Y53" s="2">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="Z53" s="2">
         <v>0</v>
       </c>
       <c r="AA53" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AB53" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AC53" s="2">
         <v>0</v>
@@ -21684,16 +21723,16 @@
         <v>10</v>
       </c>
       <c r="AY53" s="14" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="AZ53" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BA53" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BB53" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="BC53" s="2">
         <v>0</v>
@@ -21715,7 +21754,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F54" s="2">
         <v>0</v>
@@ -21730,13 +21769,13 @@
         <v>0</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>7</v>
+        <v>293</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>7</v>
@@ -21769,25 +21808,25 @@
         <v>2</v>
       </c>
       <c r="W54" s="2">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="X54" s="2">
         <v>0</v>
       </c>
       <c r="Y54" s="2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="Z54" s="2">
         <v>0</v>
       </c>
       <c r="AA54" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AB54" s="2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC54" s="2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AD54" s="2">
         <v>0</v>
@@ -21805,7 +21844,7 @@
         <v>0</v>
       </c>
       <c r="AI54" s="2">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="AJ54" s="2">
         <v>0</v>
@@ -21841,7 +21880,7 @@
         <v>0</v>
       </c>
       <c r="AU54" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AV54" s="2">
         <v>0</v>
@@ -21853,16 +21892,16 @@
         <v>10</v>
       </c>
       <c r="AY54" s="14" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="AZ54" s="2">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="BA54" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BB54" s="4" t="s">
-        <v>306</v>
+        <v>216</v>
       </c>
       <c r="BC54" s="2">
         <v>0</v>
@@ -21884,7 +21923,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -21899,10 +21938,10 @@
         <v>0</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>7</v>
@@ -21938,25 +21977,25 @@
         <v>2</v>
       </c>
       <c r="W55" s="2">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="X55" s="2">
         <v>0</v>
       </c>
       <c r="Y55" s="2">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="Z55" s="2">
         <v>0</v>
       </c>
       <c r="AA55" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AB55" s="2">
         <v>0</v>
       </c>
       <c r="AC55" s="2">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AD55" s="2">
         <v>0</v>
@@ -21974,7 +22013,7 @@
         <v>0</v>
       </c>
       <c r="AI55" s="2">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AJ55" s="2">
         <v>0</v>
@@ -22010,7 +22049,7 @@
         <v>0</v>
       </c>
       <c r="AU55" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV55" s="2">
         <v>0</v>
@@ -22022,16 +22061,16 @@
         <v>10</v>
       </c>
       <c r="AY55" s="14" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="AZ55" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="BA55" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="BB55" s="4" t="s">
-        <v>218</v>
+        <v>306</v>
       </c>
       <c r="BC55" s="2">
         <v>0</v>
@@ -22068,10 +22107,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>7</v>
@@ -22107,7 +22146,7 @@
         <v>2</v>
       </c>
       <c r="W56" s="2">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="X56" s="2">
         <v>0</v>
@@ -22191,16 +22230,16 @@
         <v>10</v>
       </c>
       <c r="AY56" s="14" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AZ56" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA56" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BB56" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BC56" s="2">
         <v>0</v>
@@ -22219,10 +22258,10 @@
         <v>0</v>
       </c>
       <c r="D57" s="2">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="E57" s="2">
-        <v>9999</v>
+        <v>20</v>
       </c>
       <c r="F57" s="2">
         <v>0</v>
@@ -22237,10 +22276,10 @@
         <v>0</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>7</v>
+        <v>175</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>7</v>
@@ -22264,7 +22303,7 @@
         <v>7</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="T57" s="2">
         <v>0</v>
@@ -22273,16 +22312,16 @@
         <v>1</v>
       </c>
       <c r="V57" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W57" s="2">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="X57" s="2">
         <v>0</v>
       </c>
       <c r="Y57" s="2">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="Z57" s="2">
         <v>0</v>
@@ -22291,10 +22330,10 @@
         <v>0</v>
       </c>
       <c r="AB57" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AC57" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AD57" s="2">
         <v>0</v>
@@ -22312,7 +22351,7 @@
         <v>0</v>
       </c>
       <c r="AI57" s="2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AJ57" s="2">
         <v>0</v>
@@ -22348,7 +22387,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AV57" s="2">
         <v>0</v>
@@ -22360,18 +22399,187 @@
         <v>10</v>
       </c>
       <c r="AY57" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="AZ57" s="2">
+        <v>20</v>
+      </c>
+      <c r="BA57" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="BB57" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="BC57" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="B58" s="2">
+        <f t="shared" si="3"/>
+        <v>10056</v>
+      </c>
+      <c r="C58" s="2">
+        <v>0</v>
+      </c>
+      <c r="D58" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E58" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T58" s="2">
+        <v>0</v>
+      </c>
+      <c r="U58" s="2">
+        <v>1</v>
+      </c>
+      <c r="V58" s="2">
+        <v>1</v>
+      </c>
+      <c r="W58" s="2">
+        <v>300</v>
+      </c>
+      <c r="X58" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="2">
+        <v>54</v>
+      </c>
+      <c r="Z58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="2">
+        <v>50</v>
+      </c>
+      <c r="AJ58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU58" s="2">
+        <v>5</v>
+      </c>
+      <c r="AV58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW58" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX58" s="2">
+        <v>10</v>
+      </c>
+      <c r="AY58" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="AZ57" s="2">
+      <c r="AZ58" s="2">
         <v>13</v>
       </c>
-      <c r="BA57" s="5" t="s">
+      <c r="BA58" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="BB57" s="4" t="s">
+      <c r="BB58" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BC57" s="2">
+      <c r="BC58" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C39F75-CA62-4F21-BA3E-9A63C334176A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C7B376-0006-4589-92F1-6B2EEA331E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2445" yWindow="885" windowWidth="25485" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2325" yWindow="1170" windowWidth="25485" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="369">
   <si>
     <t>desc</t>
   </si>
@@ -2678,24 +2678,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>アップルパイが食べたい！</t>
-    <rPh sb="7" eb="8">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
-さくさくのアップルパイが欲しいそうだわ。</t>
-    <rPh sb="38" eb="40">
-      <t>イライ</t>
-    </rPh>
-    <rPh sb="55" eb="56">
-      <t>ホ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>Chocolate</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2812,32 +2794,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
-誕生日会で大きい派手なお菓子を飾りたいみたい。</t>
-    <rPh sb="38" eb="40">
-      <t>イライ</t>
-    </rPh>
-    <rPh sb="43" eb="46">
-      <t>タンジョウビ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="51" eb="53">
-      <t>ハデ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>カシ</t>
-    </rPh>
-    <rPh sb="58" eb="59">
-      <t>カザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>東洋の貿易商</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -3116,6 +3072,58 @@
     </rPh>
     <rPh sb="54" eb="55">
       <t>モ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>a_FrozenFruits</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>タルト・オ・ポムが食べたい！</t>
+    <rPh sb="9" eb="10">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;クララおばさん&lt;/color&gt;からのご依頼ね。
+さくさくのタルト・オ・ポムが欲しいそうだわ。</t>
+    <rPh sb="38" eb="40">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>百貨店</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;百貨店&lt;/color&gt;からのご依頼ね。
+イベント用に大きい派手なお菓子を飾りたいみたい。</t>
+    <rPh sb="19" eb="22">
+      <t>ヒャッカテン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="45" eb="46">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>ハデ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>カシ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>カザ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -3223,7 +3231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3259,14 +3267,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -3635,13 +3635,13 @@
         <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>30</v>
@@ -3656,19 +3656,19 @@
         <v>284</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>24</v>
@@ -12803,13 +12803,13 @@
         <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>30</v>
@@ -12824,19 +12824,19 @@
         <v>284</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>24</v>
@@ -13620,7 +13620,7 @@
         <v>36</v>
       </c>
       <c r="BB5" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="BC5" s="2">
         <v>0</v>
@@ -17794,10 +17794,10 @@
         <v>0</v>
       </c>
       <c r="AK30" s="22" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AL30" s="22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AM30" s="22" t="s">
         <v>7</v>
@@ -19578,7 +19578,7 @@
         <v>309</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>7</v>
+        <v>364</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>7</v>
@@ -19710,172 +19710,172 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:55" s="32" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="27">
+    <row r="42" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="B42" s="27">
+      <c r="B42" s="2">
         <f t="shared" si="3"/>
         <v>10040</v>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="2">
         <v>1</v>
       </c>
-      <c r="D42" s="27">
-        <v>0</v>
-      </c>
-      <c r="E42" s="27">
+      <c r="D42" s="2">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2">
         <v>15</v>
       </c>
-      <c r="F42" s="27">
-        <v>0</v>
-      </c>
-      <c r="G42" s="27">
-        <v>0</v>
-      </c>
-      <c r="H42" s="27">
-        <v>0</v>
-      </c>
-      <c r="I42" s="27">
-        <v>0</v>
-      </c>
-      <c r="J42" s="27" t="s">
-        <v>364</v>
-      </c>
-      <c r="K42" s="27" t="s">
-        <v>364</v>
-      </c>
-      <c r="L42" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="M42" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="N42" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="O42" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="P42" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q42" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="R42" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="S42" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="T42" s="27">
-        <v>0</v>
-      </c>
-      <c r="U42" s="27">
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T42" s="2">
+        <v>0</v>
+      </c>
+      <c r="U42" s="2">
         <v>1</v>
       </c>
-      <c r="V42" s="27">
+      <c r="V42" s="2">
         <v>4</v>
       </c>
-      <c r="W42" s="27">
-        <v>450</v>
-      </c>
-      <c r="X42" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="27">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AI42" s="27">
+      <c r="W42" s="2">
+        <v>390</v>
+      </c>
+      <c r="X42" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="2">
         <v>50</v>
       </c>
-      <c r="AJ42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL42" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM42" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN42" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO42" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AQ42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AR42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AS42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AT42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AU42" s="27">
+      <c r="AJ42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU42" s="2">
         <v>3</v>
       </c>
-      <c r="AV42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AW42" s="27">
-        <v>0</v>
-      </c>
-      <c r="AX42" s="27">
+      <c r="AV42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW42" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX42" s="2">
         <v>10</v>
       </c>
-      <c r="AY42" s="29" t="s">
+      <c r="AY42" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="AZ42" s="27">
+      <c r="AZ42" s="2">
         <v>100</v>
       </c>
-      <c r="BA42" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="BB42" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="BC42" s="27">
+      <c r="BA42" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="BB42" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="BC42" s="2">
         <v>0</v>
       </c>
     </row>
@@ -22647,13 +22647,13 @@
         <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>30</v>
@@ -22668,19 +22668,19 @@
         <v>284</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>24</v>
@@ -23197,13 +23197,13 @@
         <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>30</v>
@@ -23218,19 +23218,19 @@
         <v>284</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>24</v>
@@ -24011,10 +24011,10 @@
         <v>3</v>
       </c>
       <c r="BA5" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="BB5" s="4" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="BC5" s="3">
         <v>0</v>
@@ -24051,19 +24051,19 @@
         <v>0</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="M6" s="21" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="N6" s="21" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O6" s="21" t="s">
         <v>7</v>
@@ -24135,10 +24135,10 @@
         <v>136</v>
       </c>
       <c r="AL6" s="22" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AM6" s="22" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AN6" s="22" t="s">
         <v>7</v>
@@ -24174,16 +24174,16 @@
         <v>30</v>
       </c>
       <c r="AY6" s="23" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AZ6" s="21">
         <v>23</v>
       </c>
       <c r="BA6" s="24" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="BB6" s="25" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="BC6" s="22">
         <v>0</v>
@@ -24349,10 +24349,10 @@
         <v>9</v>
       </c>
       <c r="BA7" s="5" t="s">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="BB7" s="4" t="s">
-        <v>313</v>
+        <v>366</v>
       </c>
       <c r="BC7" s="3">
         <v>0</v>
@@ -24389,10 +24389,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>7</v>
@@ -24512,16 +24512,16 @@
         <v>30</v>
       </c>
       <c r="AY8" s="14" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AZ8" s="2">
         <v>23</v>
       </c>
       <c r="BA8" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="BB8" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="BC8" s="3">
         <v>0</v>
@@ -24558,7 +24558,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K9" s="21" t="s">
         <v>7</v>
@@ -24585,7 +24585,7 @@
         <v>7</v>
       </c>
       <c r="S9" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="T9" s="21">
         <v>0</v>
@@ -24681,16 +24681,16 @@
         <v>30</v>
       </c>
       <c r="AY9" s="23" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AZ9" s="21">
         <v>22</v>
       </c>
       <c r="BA9" s="24" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="BB9" s="25" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="BC9" s="22">
         <v>0</v>
@@ -24727,13 +24727,13 @@
         <v>0</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M10" s="21" t="s">
         <v>7</v>
@@ -24850,16 +24850,16 @@
         <v>30</v>
       </c>
       <c r="AY10" s="23" t="s">
-        <v>257</v>
+        <v>367</v>
       </c>
       <c r="AZ10" s="21">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="BA10" s="24" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="BB10" s="25" t="s">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="BC10" s="22">
         <v>0</v>
@@ -24896,10 +24896,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>7</v>
@@ -25019,16 +25019,16 @@
         <v>30</v>
       </c>
       <c r="AY11" s="14" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AZ11" s="2">
         <v>23</v>
       </c>
       <c r="BA11" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="BB11" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="BC11" s="3">
         <v>0</v>
@@ -25065,7 +25065,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>7</v>
@@ -25092,7 +25092,7 @@
         <v>7</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="T12" s="2">
         <v>0</v>
@@ -25194,10 +25194,10 @@
         <v>16</v>
       </c>
       <c r="BA12" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="BB12" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="BC12" s="3">
         <v>0</v>
@@ -25234,10 +25234,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>7</v>
@@ -25357,16 +25357,16 @@
         <v>30</v>
       </c>
       <c r="AY13" s="14" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AZ13" s="2">
         <v>18</v>
       </c>
       <c r="BA13" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="BB13" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="BC13" s="3">
         <v>0</v>
@@ -25604,13 +25604,13 @@
         <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>30</v>
@@ -25625,19 +25625,19 @@
         <v>284</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>24</v>
@@ -26152,13 +26152,13 @@
         <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>30</v>
@@ -26173,19 +26173,19 @@
         <v>284</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>24</v>
@@ -26499,7 +26499,7 @@
         <v>300</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K3" s="21" t="s">
         <v>7</v>
@@ -26526,7 +26526,7 @@
         <v>7</v>
       </c>
       <c r="S3" s="21" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="T3" s="21">
         <v>0</v>
@@ -26622,16 +26622,16 @@
         <v>100</v>
       </c>
       <c r="AY3" s="23" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AZ3" s="21">
         <v>22</v>
       </c>
       <c r="BA3" s="24" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="BB3" s="25" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="BC3" s="22">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C7B376-0006-4589-92F1-6B2EEA331E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07757795-98FB-4A7C-91AE-C62D4CDC0636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="1170" windowWidth="25485" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2220" yWindow="780" windowWidth="25485" windowHeight="14370" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -24189,172 +24189,172 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
+    <row r="7" spans="1:55" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="21">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="21">
         <f t="shared" si="1"/>
         <v>30005</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T7" s="2">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2">
+      <c r="C7" s="21">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21">
+        <v>0</v>
+      </c>
+      <c r="E7" s="21">
+        <v>11</v>
+      </c>
+      <c r="F7" s="21">
+        <v>0</v>
+      </c>
+      <c r="G7" s="21">
         <v>1</v>
       </c>
-      <c r="V7" s="2">
+      <c r="H7" s="21">
+        <v>0</v>
+      </c>
+      <c r="I7" s="21">
+        <v>0</v>
+      </c>
+      <c r="J7" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="O7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="P7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="S7" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="T7" s="21">
+        <v>0</v>
+      </c>
+      <c r="U7" s="21">
         <v>1</v>
       </c>
-      <c r="W7" s="2">
-        <v>2200</v>
-      </c>
-      <c r="X7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>54</v>
-      </c>
-      <c r="Z7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB7" s="2">
-        <v>90</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="2">
+      <c r="V7" s="21">
+        <v>1</v>
+      </c>
+      <c r="W7" s="21">
+        <v>1300</v>
+      </c>
+      <c r="X7" s="21">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="21">
+        <v>80</v>
+      </c>
+      <c r="Z7" s="21">
+        <v>120</v>
+      </c>
+      <c r="AA7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="21">
+        <v>70</v>
+      </c>
+      <c r="AE7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="21">
         <v>50</v>
       </c>
-      <c r="AJ7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT7" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="2">
-        <v>8</v>
-      </c>
-      <c r="AV7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX7" s="2">
+      <c r="AJ7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL7" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM7" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN7" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO7" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="21">
+        <v>10</v>
+      </c>
+      <c r="AV7" s="22">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="22">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="21">
         <v>30</v>
       </c>
-      <c r="AY7" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="AZ7" s="2">
-        <v>9</v>
-      </c>
-      <c r="BA7" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="BB7" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="BC7" s="3">
+      <c r="AY7" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="AZ7" s="21">
+        <v>22</v>
+      </c>
+      <c r="BA7" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="BB7" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="BC7" s="22">
         <v>0</v>
       </c>
     </row>
@@ -24374,7 +24374,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -24389,10 +24389,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>7</v>
@@ -24428,44 +24428,44 @@
         <v>1</v>
       </c>
       <c r="W8" s="2">
-        <v>8000</v>
+        <v>2200</v>
       </c>
       <c r="X8" s="2">
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="Z8" s="2">
         <v>0</v>
       </c>
       <c r="AA8" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>90</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="2">
         <v>50</v>
       </c>
-      <c r="AB8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>100</v>
-      </c>
-      <c r="AD8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="2">
-        <v>80</v>
-      </c>
       <c r="AJ8" s="2">
         <v>0</v>
       </c>
@@ -24500,7 +24500,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV8" s="3">
         <v>0</v>
@@ -24512,187 +24512,187 @@
         <v>30</v>
       </c>
       <c r="AY8" s="14" t="s">
-        <v>336</v>
+        <v>257</v>
       </c>
       <c r="AZ8" s="2">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="BA8" s="5" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="BB8" s="4" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="BC8" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:55" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="21">
+    <row r="9" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="2">
         <f t="shared" si="1"/>
         <v>30007</v>
       </c>
-      <c r="C9" s="21">
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
-        <v>0</v>
-      </c>
-      <c r="E9" s="21">
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
         <v>15</v>
       </c>
-      <c r="F9" s="21">
-        <v>0</v>
-      </c>
-      <c r="G9" s="21">
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2">
         <v>1</v>
       </c>
-      <c r="H9" s="21">
-        <v>0</v>
-      </c>
-      <c r="I9" s="21">
-        <v>0</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>313</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="M9" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="N9" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="O9" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="P9" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q9" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="R9" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="S9" s="21" t="s">
-        <v>312</v>
-      </c>
-      <c r="T9" s="21">
-        <v>0</v>
-      </c>
-      <c r="U9" s="21">
+      <c r="V9" s="2">
         <v>1</v>
       </c>
-      <c r="V9" s="21">
-        <v>1</v>
-      </c>
-      <c r="W9" s="21">
-        <v>1300</v>
-      </c>
-      <c r="X9" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="21">
+      <c r="W9" s="2">
+        <v>8000</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>180</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>100</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="2">
         <v>80</v>
       </c>
-      <c r="Z9" s="21">
-        <v>120</v>
-      </c>
-      <c r="AA9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="21">
-        <v>70</v>
-      </c>
-      <c r="AE9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="21">
-        <v>50</v>
-      </c>
-      <c r="AJ9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL9" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM9" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN9" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO9" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="21">
-        <v>10</v>
-      </c>
-      <c r="AV9" s="22">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="22">
-        <v>0</v>
-      </c>
-      <c r="AX9" s="21">
+      <c r="AJ9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="2">
+        <v>12</v>
+      </c>
+      <c r="AV9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="2">
         <v>30</v>
       </c>
-      <c r="AY9" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="AZ9" s="21">
-        <v>22</v>
-      </c>
-      <c r="BA9" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="BB9" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="BC9" s="22">
+      <c r="AY9" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="AZ9" s="2">
+        <v>23</v>
+      </c>
+      <c r="BA9" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="BB9" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="BC9" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07757795-98FB-4A7C-91AE-C62D4CDC0636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D891D52E-D69A-4D66-8051-63F2FD9E4356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2220" yWindow="780" windowWidth="25485" windowHeight="14370" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25005" windowHeight="14370" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="372">
   <si>
     <t>desc</t>
   </si>
@@ -3125,6 +3125,18 @@
     <rPh sb="55" eb="56">
       <t>カザ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>a_GlowCookie</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>a_GlowCookieFruits</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>a_CookieCake</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -24066,13 +24078,13 @@
         <v>353</v>
       </c>
       <c r="O6" s="21" t="s">
-        <v>7</v>
+        <v>369</v>
       </c>
       <c r="P6" s="21" t="s">
-        <v>7</v>
+        <v>370</v>
       </c>
       <c r="Q6" s="21" t="s">
-        <v>7</v>
+        <v>371</v>
       </c>
       <c r="R6" s="21" t="s">
         <v>7</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D891D52E-D69A-4D66-8051-63F2FD9E4356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F3E3B6-AB8F-4AF9-AB01-6CFEE4ABC39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25005" windowHeight="14370" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2430" yWindow="1065" windowWidth="25005" windowHeight="14370" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="390">
   <si>
     <t>desc</t>
   </si>
@@ -3137,6 +3137,157 @@
   </si>
   <si>
     <t>a_CookieCake</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>maffin_banana</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バナナマフィンが食べたい</t>
+    <rPh sb="8" eb="9">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;バナナ好きなメイドさん&lt;/color&gt;からのご依頼ね。
+バナナをのせたマフィンが食べたいみたい。</t>
+    <rPh sb="22" eb="23">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mint_ice_cream</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>icecream_mint</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ミントアイスクリームが食べたい！</t>
+    <rPh sb="11" eb="12">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;ご婦人&lt;/color&gt;の方からのご依頼ね。
+とてもきれいなミント色のアイスを食べてみたいそうよ。</t>
+    <rPh sb="20" eb="22">
+      <t>フジン</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="51" eb="52">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Mint</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>choco_banana_crepe</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>crepe_chocobanana</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコバナナクレープが食べたい！</t>
+    <rPh sb="11" eb="12">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;メイド学校の先生&lt;/color&gt;の方からのご依頼ね。
+メイドカフェの目玉となる商品がほしいそうよ。</t>
+    <rPh sb="22" eb="24">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>メダマ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ショウヒン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>WhipeedCream</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>choco_banana_pan_cake</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>pan_cake_choco_banana</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チョコバナナパンケーキが食べたい！</t>
+    <rPh sb="12" eb="13">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;メイド学校の先生&lt;/color&gt;の方からのご依頼ね。
+カフェのイベント用に特別なデザートが欲しいみたい。</t>
+    <rPh sb="22" eb="24">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センセイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>トクベツ</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>ホ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GlowBanana</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -12763,7 +12914,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BC58"/>
+  <dimension ref="A1:BC59"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
@@ -18372,11 +18523,11 @@
     </row>
     <row r="34" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <f t="shared" ref="A34:A58" si="2">ROW()-2</f>
+        <f t="shared" ref="A34:A59" si="2">ROW()-2</f>
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <f t="shared" ref="B34:B58" si="3">(ROW()-2)+10000</f>
+        <f t="shared" ref="B34:B59" si="3">(ROW()-2)+10000</f>
         <v>10032</v>
       </c>
       <c r="C34" s="2">
@@ -22439,10 +22590,10 @@
         <v>0</v>
       </c>
       <c r="D58" s="2">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="E58" s="2">
-        <v>9999</v>
+        <v>25</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
@@ -22457,10 +22608,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>20</v>
+        <v>372</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>7</v>
+        <v>372</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>7</v>
@@ -22484,7 +22635,7 @@
         <v>7</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="T58" s="2">
         <v>0</v>
@@ -22493,16 +22644,16 @@
         <v>1</v>
       </c>
       <c r="V58" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W58" s="2">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="X58" s="2">
         <v>0</v>
       </c>
       <c r="Y58" s="2">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="Z58" s="2">
         <v>0</v>
@@ -22511,10 +22662,10 @@
         <v>0</v>
       </c>
       <c r="AB58" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AD58" s="2">
         <v>0</v>
@@ -22532,7 +22683,7 @@
         <v>0</v>
       </c>
       <c r="AI58" s="2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AJ58" s="2">
         <v>0</v>
@@ -22568,7 +22719,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AV58" s="2">
         <v>0</v>
@@ -22580,18 +22731,187 @@
         <v>10</v>
       </c>
       <c r="AY58" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ58" s="2">
+        <v>100</v>
+      </c>
+      <c r="BA58" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="BB58" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="BC58" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="B59" s="2">
+        <f t="shared" si="3"/>
+        <v>10057</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0</v>
+      </c>
+      <c r="D59" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E59" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="2">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2">
+        <v>0</v>
+      </c>
+      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T59" s="2">
+        <v>0</v>
+      </c>
+      <c r="U59" s="2">
+        <v>1</v>
+      </c>
+      <c r="V59" s="2">
+        <v>1</v>
+      </c>
+      <c r="W59" s="2">
+        <v>300</v>
+      </c>
+      <c r="X59" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="2">
+        <v>54</v>
+      </c>
+      <c r="Z59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="2">
+        <v>50</v>
+      </c>
+      <c r="AJ59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU59" s="2">
+        <v>5</v>
+      </c>
+      <c r="AV59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW59" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX59" s="2">
+        <v>10</v>
+      </c>
+      <c r="AY59" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="AZ58" s="2">
+      <c r="AZ59" s="2">
         <v>13</v>
       </c>
-      <c r="BA58" s="5" t="s">
+      <c r="BA59" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="BB58" s="4" t="s">
+      <c r="BB59" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BC58" s="2">
+      <c r="BC59" s="2">
         <v>1</v>
       </c>
     </row>
@@ -23156,7 +23476,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BC14"/>
+  <dimension ref="A1:BC17"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
@@ -23358,11 +23678,11 @@
     </row>
     <row r="2" spans="1:55" s="10" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
-        <f t="shared" ref="A2:A14" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A17" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="7">
-        <f t="shared" ref="B2:B13" si="1">(ROW()-2)+30000</f>
+        <f t="shared" ref="B2:B16" si="1">(ROW()-2)+30000</f>
         <v>30000</v>
       </c>
       <c r="C2" s="7">
@@ -23527,7 +23847,7 @@
     </row>
     <row r="3" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A13" si="2">ROW()-2</f>
+        <f t="shared" ref="A3:A16" si="2">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="2">
@@ -24032,172 +24352,172 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:55" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="21">
+    <row r="6" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="2">
         <f t="shared" si="1"/>
         <v>30004</v>
       </c>
-      <c r="C6" s="21">
-        <v>0</v>
-      </c>
-      <c r="D6" s="21">
-        <v>0</v>
-      </c>
-      <c r="E6" s="21">
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
         <v>11</v>
       </c>
-      <c r="F6" s="21">
-        <v>0</v>
-      </c>
-      <c r="G6" s="21">
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2">
         <v>1</v>
       </c>
-      <c r="H6" s="21">
-        <v>0</v>
-      </c>
-      <c r="I6" s="21">
-        <v>0</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="K6" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="L6" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="M6" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="N6" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="O6" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="P6" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q6" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="R6" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="S6" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="T6" s="21">
-        <v>0</v>
-      </c>
-      <c r="U6" s="21">
+      <c r="V6" s="2">
         <v>1</v>
       </c>
-      <c r="V6" s="21">
-        <v>1</v>
-      </c>
-      <c r="W6" s="21">
-        <v>1000</v>
-      </c>
-      <c r="X6" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="21">
-        <v>32</v>
-      </c>
-      <c r="Z6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="21">
-        <v>60</v>
-      </c>
-      <c r="AC6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="21">
+      <c r="W6" s="2">
+        <v>1200</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2">
         <v>50</v>
       </c>
-      <c r="AJ6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="AL6" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="AM6" s="22" t="s">
-        <v>350</v>
-      </c>
-      <c r="AN6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP6" s="21">
-        <v>50</v>
-      </c>
-      <c r="AQ6" s="21">
-        <v>50</v>
-      </c>
-      <c r="AR6" s="21">
-        <v>50</v>
-      </c>
-      <c r="AS6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="21">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="22">
-        <v>0</v>
-      </c>
-      <c r="AW6" s="22">
-        <v>0</v>
-      </c>
-      <c r="AX6" s="21">
+      <c r="AE6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="AM6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP6" s="2">
+        <v>25</v>
+      </c>
+      <c r="AQ6" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="2">
+        <v>13</v>
+      </c>
+      <c r="AV6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX6" s="2">
         <v>30</v>
       </c>
-      <c r="AY6" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="AZ6" s="21">
-        <v>23</v>
-      </c>
-      <c r="BA6" s="24" t="s">
-        <v>339</v>
-      </c>
-      <c r="BB6" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="BC6" s="22">
+      <c r="AY6" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="AZ6" s="2">
+        <v>19</v>
+      </c>
+      <c r="BA6" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="BB6" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="BC6" s="3">
         <v>0</v>
       </c>
     </row>
@@ -24232,34 +24552,34 @@
         <v>0</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>7</v>
+        <v>355</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>7</v>
+        <v>351</v>
       </c>
       <c r="M7" s="21" t="s">
-        <v>7</v>
+        <v>352</v>
       </c>
       <c r="N7" s="21" t="s">
-        <v>7</v>
+        <v>353</v>
       </c>
       <c r="O7" s="21" t="s">
-        <v>7</v>
+        <v>369</v>
       </c>
       <c r="P7" s="21" t="s">
-        <v>7</v>
+        <v>370</v>
       </c>
       <c r="Q7" s="21" t="s">
-        <v>7</v>
+        <v>371</v>
       </c>
       <c r="R7" s="21" t="s">
         <v>7</v>
       </c>
       <c r="S7" s="21" t="s">
-        <v>312</v>
+        <v>7</v>
       </c>
       <c r="T7" s="21">
         <v>0</v>
@@ -24271,28 +24591,28 @@
         <v>1</v>
       </c>
       <c r="W7" s="21">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="X7" s="21">
         <v>0</v>
       </c>
       <c r="Y7" s="21">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="Z7" s="21">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="21">
         <v>0</v>
       </c>
       <c r="AB7" s="21">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AC7" s="21">
         <v>0</v>
       </c>
       <c r="AD7" s="21">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="21">
         <v>0</v>
@@ -24313,13 +24633,13 @@
         <v>0</v>
       </c>
       <c r="AK7" s="22" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="AL7" s="22" t="s">
-        <v>7</v>
+        <v>344</v>
       </c>
       <c r="AM7" s="22" t="s">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="AN7" s="22" t="s">
         <v>7</v>
@@ -24328,13 +24648,13 @@
         <v>7</v>
       </c>
       <c r="AP7" s="21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AQ7" s="21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR7" s="21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AS7" s="21">
         <v>0</v>
@@ -24343,7 +24663,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV7" s="22">
         <v>0</v>
@@ -24355,187 +24675,187 @@
         <v>30</v>
       </c>
       <c r="AY7" s="23" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AZ7" s="21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA7" s="24" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="BB7" s="25" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="BC7" s="22">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
+    <row r="8" spans="1:55" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="21">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="21">
         <f t="shared" si="1"/>
         <v>30006</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
-        <v>13</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T8" s="2">
-        <v>0</v>
-      </c>
-      <c r="U8" s="2">
+      <c r="C8" s="21">
+        <v>0</v>
+      </c>
+      <c r="D8" s="21">
+        <v>0</v>
+      </c>
+      <c r="E8" s="21">
+        <v>11</v>
+      </c>
+      <c r="F8" s="21">
+        <v>0</v>
+      </c>
+      <c r="G8" s="21">
         <v>1</v>
       </c>
-      <c r="V8" s="2">
+      <c r="H8" s="21">
+        <v>0</v>
+      </c>
+      <c r="I8" s="21">
+        <v>0</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="O8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="P8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="R8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="S8" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="T8" s="21">
+        <v>0</v>
+      </c>
+      <c r="U8" s="21">
         <v>1</v>
       </c>
-      <c r="W8" s="2">
-        <v>2200</v>
-      </c>
-      <c r="X8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>54</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB8" s="2">
-        <v>90</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="2">
+      <c r="V8" s="21">
+        <v>1</v>
+      </c>
+      <c r="W8" s="21">
+        <v>1300</v>
+      </c>
+      <c r="X8" s="21">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="21">
+        <v>80</v>
+      </c>
+      <c r="Z8" s="21">
+        <v>120</v>
+      </c>
+      <c r="AA8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="21">
+        <v>70</v>
+      </c>
+      <c r="AE8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="21">
         <v>50</v>
       </c>
-      <c r="AJ8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="2">
-        <v>8</v>
-      </c>
-      <c r="AV8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX8" s="2">
+      <c r="AJ8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL8" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM8" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN8" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO8" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="21">
+        <v>10</v>
+      </c>
+      <c r="AV8" s="22">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="22">
+        <v>0</v>
+      </c>
+      <c r="AX8" s="21">
         <v>30</v>
       </c>
-      <c r="AY8" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="AZ8" s="2">
-        <v>9</v>
-      </c>
-      <c r="BA8" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="BB8" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="BC8" s="3">
+      <c r="AY8" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="AZ8" s="21">
+        <v>22</v>
+      </c>
+      <c r="BA8" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="BB8" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="BC8" s="22">
         <v>0</v>
       </c>
     </row>
@@ -24555,7 +24875,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -24570,10 +24890,10 @@
         <v>0</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>7</v>
@@ -24609,44 +24929,44 @@
         <v>1</v>
       </c>
       <c r="W9" s="2">
-        <v>8000</v>
+        <v>2200</v>
       </c>
       <c r="X9" s="2">
         <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="Z9" s="2">
         <v>0</v>
       </c>
       <c r="AA9" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>90</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="2">
         <v>50</v>
       </c>
-      <c r="AB9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="2">
-        <v>100</v>
-      </c>
-      <c r="AD9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="2">
-        <v>80</v>
-      </c>
       <c r="AJ9" s="2">
         <v>0</v>
       </c>
@@ -24681,7 +25001,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV9" s="3">
         <v>0</v>
@@ -24693,356 +25013,356 @@
         <v>30</v>
       </c>
       <c r="AY9" s="14" t="s">
-        <v>336</v>
+        <v>257</v>
       </c>
       <c r="AZ9" s="2">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="BA9" s="5" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="BB9" s="4" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="BC9" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:55" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21">
+    <row r="10" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="2">
         <f t="shared" si="1"/>
         <v>30008</v>
       </c>
-      <c r="C10" s="21">
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
-        <v>0</v>
-      </c>
-      <c r="E10" s="21">
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
         <v>15</v>
       </c>
-      <c r="F10" s="21">
-        <v>0</v>
-      </c>
-      <c r="G10" s="21">
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2">
         <v>1</v>
       </c>
-      <c r="H10" s="21">
-        <v>0</v>
-      </c>
-      <c r="I10" s="21">
-        <v>0</v>
-      </c>
-      <c r="J10" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="K10" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="L10" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="M10" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="N10" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="O10" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="P10" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q10" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="R10" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="S10" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="T10" s="21">
-        <v>0</v>
-      </c>
-      <c r="U10" s="21">
+      <c r="V10" s="2">
         <v>1</v>
       </c>
-      <c r="V10" s="21">
-        <v>1</v>
-      </c>
-      <c r="W10" s="21">
-        <v>2700</v>
-      </c>
-      <c r="X10" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="21">
+      <c r="W10" s="2">
+        <v>8000</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>180</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>100</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="2">
         <v>80</v>
       </c>
-      <c r="Z10" s="21">
-        <v>150</v>
-      </c>
-      <c r="AA10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="21">
-        <v>200</v>
-      </c>
-      <c r="AE10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="21">
-        <v>50</v>
-      </c>
-      <c r="AJ10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL10" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM10" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN10" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO10" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AT10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="21">
-        <v>10</v>
-      </c>
-      <c r="AV10" s="22">
-        <v>0</v>
-      </c>
-      <c r="AW10" s="22">
-        <v>0</v>
-      </c>
-      <c r="AX10" s="21">
+      <c r="AJ10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="2">
+        <v>12</v>
+      </c>
+      <c r="AV10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX10" s="2">
         <v>30</v>
       </c>
-      <c r="AY10" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="AZ10" s="21">
+      <c r="AY10" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="AZ10" s="2">
         <v>23</v>
       </c>
-      <c r="BA10" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="BB10" s="25" t="s">
-        <v>368</v>
-      </c>
-      <c r="BC10" s="22">
+      <c r="BA10" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="BB10" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="BC10" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
+    <row r="11" spans="1:55" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="21">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="21">
         <f t="shared" si="1"/>
         <v>30009</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>18</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T11" s="2">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2">
+      <c r="C11" s="21">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21">
+        <v>15</v>
+      </c>
+      <c r="F11" s="21">
+        <v>0</v>
+      </c>
+      <c r="G11" s="21">
         <v>1</v>
       </c>
-      <c r="V11" s="2">
+      <c r="H11" s="21">
+        <v>0</v>
+      </c>
+      <c r="I11" s="21">
+        <v>0</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="N11" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="P11" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="R11" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="S11" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="T11" s="21">
+        <v>0</v>
+      </c>
+      <c r="U11" s="21">
         <v>1</v>
       </c>
-      <c r="W11" s="2">
-        <v>5000</v>
-      </c>
-      <c r="X11" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>180</v>
-      </c>
-      <c r="Z11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="2">
-        <v>40</v>
-      </c>
-      <c r="AB11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="2">
-        <v>90</v>
-      </c>
-      <c r="AD11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="2">
+      <c r="V11" s="21">
+        <v>1</v>
+      </c>
+      <c r="W11" s="21">
+        <v>2700</v>
+      </c>
+      <c r="X11" s="21">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="21">
         <v>80</v>
       </c>
-      <c r="AJ11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU11" s="2">
-        <v>13</v>
-      </c>
-      <c r="AV11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX11" s="2">
+      <c r="Z11" s="21">
+        <v>150</v>
+      </c>
+      <c r="AA11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="21">
+        <v>200</v>
+      </c>
+      <c r="AE11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="21">
+        <v>50</v>
+      </c>
+      <c r="AJ11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL11" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM11" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN11" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO11" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="21">
+        <v>10</v>
+      </c>
+      <c r="AV11" s="22">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="22">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="21">
         <v>30</v>
       </c>
-      <c r="AY11" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="AZ11" s="2">
+      <c r="AY11" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="AZ11" s="21">
         <v>23</v>
       </c>
-      <c r="BA11" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="BB11" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="BC11" s="3">
+      <c r="BA11" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="BB11" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="BC11" s="22">
         <v>0</v>
       </c>
     </row>
@@ -25077,10 +25397,10 @@
         <v>0</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>7</v>
+        <v>318</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>7</v>
@@ -25104,7 +25424,7 @@
         <v>7</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>322</v>
+        <v>7</v>
       </c>
       <c r="T12" s="2">
         <v>0</v>
@@ -25116,25 +25436,25 @@
         <v>1</v>
       </c>
       <c r="W12" s="2">
-        <v>2300</v>
+        <v>5000</v>
       </c>
       <c r="X12" s="2">
         <v>0</v>
       </c>
       <c r="Y12" s="2">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="Z12" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB12" s="2">
         <v>0</v>
       </c>
       <c r="AC12" s="2">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AD12" s="2">
         <v>0</v>
@@ -25200,16 +25520,16 @@
         <v>30</v>
       </c>
       <c r="AY12" s="14" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="AZ12" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BA12" s="5" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="BB12" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="BC12" s="3">
         <v>0</v>
@@ -25231,7 +25551,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F13" s="2">
         <v>0</v>
@@ -25246,10 +25566,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>315</v>
+        <v>7</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>7</v>
@@ -25273,7 +25593,7 @@
         <v>7</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>7</v>
+        <v>322</v>
       </c>
       <c r="T13" s="2">
         <v>0</v>
@@ -25285,44 +25605,44 @@
         <v>1</v>
       </c>
       <c r="W13" s="2">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="X13" s="2">
         <v>0</v>
       </c>
       <c r="Y13" s="2">
+        <v>60</v>
+      </c>
+      <c r="Z13" s="2">
+        <v>30</v>
+      </c>
+      <c r="AA13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>130</v>
+      </c>
+      <c r="AD13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="2">
         <v>80</v>
       </c>
-      <c r="Z13" s="2">
-        <v>230</v>
-      </c>
-      <c r="AA13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="2">
-        <v>120</v>
-      </c>
-      <c r="AE13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="2">
-        <v>50</v>
-      </c>
       <c r="AJ13" s="2">
         <v>0</v>
       </c>
@@ -25357,7 +25677,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV13" s="3">
         <v>0</v>
@@ -25369,16 +25689,16 @@
         <v>30</v>
       </c>
       <c r="AY13" s="14" t="s">
-        <v>331</v>
+        <v>264</v>
       </c>
       <c r="AZ13" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA13" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="BB13" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="BC13" s="3">
         <v>0</v>
@@ -25386,21 +25706,21 @@
     </row>
     <row r="14" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <f t="shared" ref="B14" si="3">(ROW()-2)+30000</f>
+        <f t="shared" si="1"/>
         <v>30012</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
       </c>
       <c r="D14" s="2">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>9999</v>
+        <v>20</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -25415,10 +25735,10 @@
         <v>0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>20</v>
+        <v>314</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>7</v>
+        <v>315</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>7</v>
@@ -25442,7 +25762,7 @@
         <v>7</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="T14" s="2">
         <v>0</v>
@@ -25454,28 +25774,28 @@
         <v>1</v>
       </c>
       <c r="W14" s="2">
-        <v>300</v>
+        <v>2500</v>
       </c>
       <c r="X14" s="2">
         <v>0</v>
       </c>
       <c r="Y14" s="2">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="Z14" s="2">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AA14" s="2">
         <v>0</v>
       </c>
       <c r="AB14" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="2">
         <v>0</v>
       </c>
       <c r="AD14" s="2">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AE14" s="2">
         <v>0</v>
@@ -25526,30 +25846,537 @@
         <v>0</v>
       </c>
       <c r="AU14" s="2">
-        <v>5</v>
-      </c>
-      <c r="AV14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW14" s="2">
+        <v>15</v>
+      </c>
+      <c r="AV14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="3">
         <v>0</v>
       </c>
       <c r="AX14" s="2">
         <v>30</v>
       </c>
       <c r="AY14" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="AZ14" s="2">
+        <v>18</v>
+      </c>
+      <c r="BA14" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="BB14" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="BC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <f t="shared" si="1"/>
+        <v>30013</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>30</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2">
+        <v>1</v>
+      </c>
+      <c r="W15" s="2">
+        <v>1500</v>
+      </c>
+      <c r="X15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>200</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>210</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>30</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>50</v>
+      </c>
+      <c r="AD15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="AL15" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="AM15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP15" s="2">
+        <v>10</v>
+      </c>
+      <c r="AQ15" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR15" s="2">
+        <v>20</v>
+      </c>
+      <c r="AS15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="2">
+        <v>10</v>
+      </c>
+      <c r="AV15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="2">
+        <v>30</v>
+      </c>
+      <c r="AY15" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="AZ15" s="2">
+        <v>16</v>
+      </c>
+      <c r="BA15" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="BB15" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="BC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <f t="shared" si="1"/>
+        <v>30014</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>30</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T16" s="2">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2">
+        <v>1</v>
+      </c>
+      <c r="W16" s="2">
+        <v>1500</v>
+      </c>
+      <c r="X16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>120</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>60</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>60</v>
+      </c>
+      <c r="AD16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="2">
+        <v>60</v>
+      </c>
+      <c r="AJ16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="AL16" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AM16" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN16" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="AO16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP16" s="3">
+        <v>20</v>
+      </c>
+      <c r="AQ16" s="3">
+        <v>50</v>
+      </c>
+      <c r="AR16" s="3">
+        <v>30</v>
+      </c>
+      <c r="AS16" s="3">
+        <v>20</v>
+      </c>
+      <c r="AT16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="2">
+        <v>10</v>
+      </c>
+      <c r="AV16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="2">
+        <v>30</v>
+      </c>
+      <c r="AY16" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="AZ16" s="2">
+        <v>16</v>
+      </c>
+      <c r="BA16" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="BB16" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="BC16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <f t="shared" ref="B17" si="3">(ROW()-2)+30000</f>
+        <v>30015</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E17" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T17" s="2">
+        <v>0</v>
+      </c>
+      <c r="U17" s="2">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2">
+        <v>1</v>
+      </c>
+      <c r="W17" s="2">
+        <v>300</v>
+      </c>
+      <c r="X17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>54</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="2">
+        <v>50</v>
+      </c>
+      <c r="AJ17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="2">
+        <v>5</v>
+      </c>
+      <c r="AV17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="2">
+        <v>30</v>
+      </c>
+      <c r="AY17" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="AZ14" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA14" s="5" t="s">
+      <c r="AZ17" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="BB14" s="4" t="s">
+      <c r="BB17" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BC14" s="2">
+      <c r="BC17" s="2">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F3E3B6-AB8F-4AF9-AB01-6CFEE4ABC39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FB2D04-D387-4A8D-9BB1-C2D8B43BCBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="1065" windowWidth="25005" windowHeight="14370" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1665" yWindow="975" windowWidth="25005" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -13198,7 +13198,7 @@
         <v>0</v>
       </c>
       <c r="AB2" s="7">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AC2" s="7">
         <v>0</v>
@@ -13367,7 +13367,7 @@
         <v>25</v>
       </c>
       <c r="AB3" s="2">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AC3" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FB2D04-D387-4A8D-9BB1-C2D8B43BCBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED67B859-E004-4E88-AA30-97E7CA51475A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1665" yWindow="975" windowWidth="25005" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="840" windowWidth="25005" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -15887,7 +15887,7 @@
         <v>1</v>
       </c>
       <c r="W18" s="2">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="X18" s="2">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED67B859-E004-4E88-AA30-97E7CA51475A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E37CB9-51FC-41D7-B942-9F02CF13B71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="840" windowWidth="25005" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="960" windowWidth="25005" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="392">
   <si>
     <t>desc</t>
   </si>
@@ -3288,6 +3288,14 @@
   </si>
   <si>
     <t>GlowBanana</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>doubleberry_crepe</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>strawberryblueberry_crepe</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -19572,10 +19580,10 @@
         <v>162</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>7</v>
+        <v>390</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>7</v>
+        <v>391</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>7</v>
@@ -19771,7 +19779,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W41" s="2">
         <v>550</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E37CB9-51FC-41D7-B942-9F02CF13B71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468E4E27-29A9-405F-96F1-FFA28356CC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="960" windowWidth="25005" windowHeight="14370" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="1365" windowWidth="25005" windowHeight="14355" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -17262,7 +17262,7 @@
         <v>0</v>
       </c>
       <c r="AB26" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AC26" s="2">
         <v>0</v>
@@ -17304,7 +17304,7 @@
         <v>7</v>
       </c>
       <c r="AP26" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AQ26" s="2">
         <v>0</v>
@@ -17938,7 +17938,7 @@
         <v>40</v>
       </c>
       <c r="AB30" s="21">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AC30" s="21">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_QuestSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468E4E27-29A9-405F-96F1-FFA28356CC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F717451-51AB-46D4-B7EB-A35C47A34638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="1365" windowWidth="25005" windowHeight="14355" tabRatio="822" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3795" yWindow="1155" windowWidth="21915" windowHeight="13455" tabRatio="822" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_QuestSetData" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2760" uniqueCount="396">
   <si>
     <t>desc</t>
   </si>
@@ -3296,6 +3296,47 @@
   </si>
   <si>
     <t>strawberryblueberry_crepe</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>yaki_maron</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>yakiguri</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>焼き栗を食べたい！</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>クリ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>これは、&lt;color=#FF78B4&gt;近所のおじいさん&lt;/color&gt;からのご依頼ね。
+焼きたてほくほくの栗を味わってみたいそうよ。</t>
+    <rPh sb="19" eb="21">
+      <t>キンジョ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>イライ</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>クリ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>アジ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -23484,7 +23525,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:BC17"/>
+  <dimension ref="A1:BC18"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="27.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
@@ -23686,11 +23727,11 @@
     </row>
     <row r="2" spans="1:55" s="10" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
-        <f t="shared" ref="A2:A17" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A18" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="7">
-        <f t="shared" ref="B2:B16" si="1">(ROW()-2)+30000</f>
+        <f t="shared" ref="B2:B17" si="1">(ROW()-2)+30000</f>
         <v>30000</v>
       </c>
       <c r="C2" s="7">
@@ -23855,7 +23896,7 @@
     </row>
     <row r="3" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <f t="shared" ref="A3:A16" si="2">ROW()-2</f>
+        <f t="shared" ref="A3:A17" si="2">ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="2">
@@ -24038,7 +24079,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -24053,10 +24094,10 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>152</v>
+        <v>393</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>152</v>
+        <v>392</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>7</v>
@@ -24092,25 +24133,25 @@
         <v>1</v>
       </c>
       <c r="W4" s="2">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="X4" s="2">
         <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="Z4" s="2">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="2">
         <v>0</v>
       </c>
       <c r="AB4" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC4" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AD4" s="2">
         <v>0</v>
@@ -24128,7 +24169,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="2">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AJ4" s="2">
         <v>0</v>
@@ -24148,46 +24189,46 @@
       <c r="AO4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AP4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="3">
+      <c r="AP4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="2">
         <v>0</v>
       </c>
       <c r="AU4" s="2">
-        <v>12</v>
-      </c>
-      <c r="AV4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="3">
+        <v>3</v>
+      </c>
+      <c r="AV4" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="2">
         <v>0</v>
       </c>
       <c r="AX4" s="2">
         <v>30</v>
       </c>
       <c r="AY4" s="14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AZ4" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA4" s="5" t="s">
-        <v>153</v>
+        <v>394</v>
       </c>
       <c r="BB4" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="BC4" s="3">
+        <v>395</v>
+      </c>
+      <c r="BC4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -24207,7 +24248,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -24222,10 +24263,10 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>7</v>
@@ -24261,25 +24302,25 @@
         <v>1</v>
       </c>
       <c r="W5" s="2">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="X5" s="2">
         <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <v>210</v>
+        <v>100</v>
       </c>
       <c r="Z5" s="2">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AA5" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2">
         <v>0</v>
       </c>
       <c r="AC5" s="2">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AD5" s="2">
         <v>0</v>
@@ -24297,7 +24338,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AJ5" s="2">
         <v>0</v>
@@ -24317,23 +24358,23 @@
       <c r="AO5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AP5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT5" s="2">
+      <c r="AP5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="3">
         <v>0</v>
       </c>
       <c r="AU5" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV5" s="3">
         <v>0</v>
@@ -24345,16 +24386,16 @@
         <v>30</v>
       </c>
       <c r="AY5" s="14" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AZ5" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BA5" s="5" t="s">
-        <v>320</v>
+        <v>153</v>
       </c>
       <c r="BB5" s="4" t="s">
-        <v>338</v>
+        <v>157</v>
       </c>
       <c r="BC5" s="3">
         <v>0</v>
@@ -24391,10 +24432,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>376</v>
+        <v>300</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>7</v>
@@ -24430,28 +24471,28 @@
         <v>1</v>
       </c>
       <c r="W6" s="2">
-        <v>1200</v>
+        <v>1700</v>
       </c>
       <c r="X6" s="2">
         <v>0</v>
       </c>
       <c r="Y6" s="2">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="Z6" s="2">
         <v>0</v>
       </c>
       <c r="AA6" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB6" s="2">
         <v>0</v>
       </c>
       <c r="AC6" s="2">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AD6" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="2">
         <v>0</v>
@@ -24466,16 +24507,16 @@
         <v>0</v>
       </c>
       <c r="AI6" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ6" s="2">
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="s">
-        <v>379</v>
+        <v>7</v>
       </c>
       <c r="AL6" s="3" t="s">
-        <v>328</v>
+        <v>7</v>
       </c>
       <c r="AM6" s="3" t="s">
         <v>7</v>
@@ -24487,10 +24528,10 @@
         <v>7</v>
       </c>
       <c r="AP6" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AQ6" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR6" s="2">
         <v>0</v>
@@ -24514,187 +24555,187 @@
         <v>30</v>
       </c>
       <c r="AY6" s="14" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="AZ6" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="BA6" s="5" t="s">
-        <v>377</v>
+        <v>320</v>
       </c>
       <c r="BB6" s="4" t="s">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="BC6" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:55" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="21">
+    <row r="7" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="2">
         <f t="shared" si="1"/>
         <v>30005</v>
       </c>
-      <c r="C7" s="21">
-        <v>0</v>
-      </c>
-      <c r="D7" s="21">
-        <v>0</v>
-      </c>
-      <c r="E7" s="21">
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
         <v>11</v>
       </c>
-      <c r="F7" s="21">
-        <v>0</v>
-      </c>
-      <c r="G7" s="21">
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
         <v>1</v>
       </c>
-      <c r="H7" s="21">
-        <v>0</v>
-      </c>
-      <c r="I7" s="21">
-        <v>0</v>
-      </c>
-      <c r="J7" s="21" t="s">
-        <v>341</v>
-      </c>
-      <c r="K7" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="M7" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="N7" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="O7" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="P7" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q7" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="R7" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="S7" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="T7" s="21">
-        <v>0</v>
-      </c>
-      <c r="U7" s="21">
+      <c r="V7" s="2">
         <v>1</v>
       </c>
-      <c r="V7" s="21">
-        <v>1</v>
-      </c>
-      <c r="W7" s="21">
-        <v>1000</v>
-      </c>
-      <c r="X7" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="21">
-        <v>32</v>
-      </c>
-      <c r="Z7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="21">
-        <v>60</v>
-      </c>
-      <c r="AC7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="21">
+      <c r="W7" s="2">
+        <v>1200</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>100</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2">
         <v>50</v>
       </c>
-      <c r="AJ7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="AL7" s="22" t="s">
-        <v>344</v>
-      </c>
-      <c r="AM7" s="22" t="s">
-        <v>350</v>
-      </c>
-      <c r="AN7" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO7" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP7" s="21">
-        <v>50</v>
-      </c>
-      <c r="AQ7" s="21">
-        <v>50</v>
-      </c>
-      <c r="AR7" s="21">
-        <v>50</v>
-      </c>
-      <c r="AS7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AT7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="21">
-        <v>8</v>
-      </c>
-      <c r="AV7" s="22">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="22">
-        <v>0</v>
-      </c>
-      <c r="AX7" s="21">
+      <c r="AE7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="2">
+        <v>100</v>
+      </c>
+      <c r="AJ7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="AL7" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="AM7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP7" s="2">
+        <v>25</v>
+      </c>
+      <c r="AQ7" s="2">
+        <v>20</v>
+      </c>
+      <c r="AR7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="2">
+        <v>13</v>
+      </c>
+      <c r="AV7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX7" s="2">
         <v>30</v>
       </c>
-      <c r="AY7" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="AZ7" s="21">
-        <v>23</v>
-      </c>
-      <c r="BA7" s="24" t="s">
-        <v>339</v>
-      </c>
-      <c r="BB7" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="BC7" s="22">
+      <c r="AY7" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="AZ7" s="2">
+        <v>19</v>
+      </c>
+      <c r="BA7" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="BB7" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="BC7" s="3">
         <v>0</v>
       </c>
     </row>
@@ -24729,34 +24770,34 @@
         <v>0</v>
       </c>
       <c r="J8" s="21" t="s">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>7</v>
+        <v>355</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>7</v>
+        <v>351</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>7</v>
+        <v>352</v>
       </c>
       <c r="N8" s="21" t="s">
-        <v>7</v>
+        <v>353</v>
       </c>
       <c r="O8" s="21" t="s">
-        <v>7</v>
+        <v>369</v>
       </c>
       <c r="P8" s="21" t="s">
-        <v>7</v>
+        <v>370</v>
       </c>
       <c r="Q8" s="21" t="s">
-        <v>7</v>
+        <v>371</v>
       </c>
       <c r="R8" s="21" t="s">
         <v>7</v>
       </c>
       <c r="S8" s="21" t="s">
-        <v>312</v>
+        <v>7</v>
       </c>
       <c r="T8" s="21">
         <v>0</v>
@@ -24768,28 +24809,28 @@
         <v>1</v>
       </c>
       <c r="W8" s="21">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="X8" s="21">
         <v>0</v>
       </c>
       <c r="Y8" s="21">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="Z8" s="21">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AA8" s="21">
         <v>0</v>
       </c>
       <c r="AB8" s="21">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AC8" s="21">
         <v>0</v>
       </c>
       <c r="AD8" s="21">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="21">
         <v>0</v>
@@ -24810,13 +24851,13 @@
         <v>0</v>
       </c>
       <c r="AK8" s="22" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="AL8" s="22" t="s">
-        <v>7</v>
+        <v>344</v>
       </c>
       <c r="AM8" s="22" t="s">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="AN8" s="22" t="s">
         <v>7</v>
@@ -24825,13 +24866,13 @@
         <v>7</v>
       </c>
       <c r="AP8" s="21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AQ8" s="21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR8" s="21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AS8" s="21">
         <v>0</v>
@@ -24840,7 +24881,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV8" s="22">
         <v>0</v>
@@ -24852,187 +24893,187 @@
         <v>30</v>
       </c>
       <c r="AY8" s="23" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AZ8" s="21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA8" s="24" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="BB8" s="25" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="BC8" s="22">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
+    <row r="9" spans="1:55" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="21">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="21">
         <f t="shared" si="1"/>
         <v>30007</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>13</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T9" s="2">
-        <v>0</v>
-      </c>
-      <c r="U9" s="2">
+      <c r="C9" s="21">
+        <v>0</v>
+      </c>
+      <c r="D9" s="21">
+        <v>0</v>
+      </c>
+      <c r="E9" s="21">
+        <v>11</v>
+      </c>
+      <c r="F9" s="21">
+        <v>0</v>
+      </c>
+      <c r="G9" s="21">
         <v>1</v>
       </c>
-      <c r="V9" s="2">
+      <c r="H9" s="21">
+        <v>0</v>
+      </c>
+      <c r="I9" s="21">
+        <v>0</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="P9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="R9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="S9" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="T9" s="21">
+        <v>0</v>
+      </c>
+      <c r="U9" s="21">
         <v>1</v>
       </c>
-      <c r="W9" s="2">
-        <v>2200</v>
-      </c>
-      <c r="X9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>54</v>
-      </c>
-      <c r="Z9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB9" s="2">
-        <v>90</v>
-      </c>
-      <c r="AC9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="2">
+      <c r="V9" s="21">
+        <v>1</v>
+      </c>
+      <c r="W9" s="21">
+        <v>1300</v>
+      </c>
+      <c r="X9" s="21">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="21">
+        <v>80</v>
+      </c>
+      <c r="Z9" s="21">
+        <v>120</v>
+      </c>
+      <c r="AA9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="21">
+        <v>70</v>
+      </c>
+      <c r="AE9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="21">
         <v>50</v>
       </c>
-      <c r="AJ9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="2">
-        <v>8</v>
-      </c>
-      <c r="AV9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX9" s="2">
+      <c r="AJ9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL9" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM9" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN9" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO9" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="21">
+        <v>10</v>
+      </c>
+      <c r="AV9" s="22">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="22">
+        <v>0</v>
+      </c>
+      <c r="AX9" s="21">
         <v>30</v>
       </c>
-      <c r="AY9" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="AZ9" s="2">
-        <v>9</v>
-      </c>
-      <c r="BA9" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="BB9" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="BC9" s="3">
+      <c r="AY9" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="AZ9" s="21">
+        <v>22</v>
+      </c>
+      <c r="BA9" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="BB9" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="BC9" s="22">
         <v>0</v>
       </c>
     </row>
@@ -25052,7 +25093,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -25067,10 +25108,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>7</v>
@@ -25106,44 +25147,44 @@
         <v>1</v>
       </c>
       <c r="W10" s="2">
-        <v>8000</v>
+        <v>2200</v>
       </c>
       <c r="X10" s="2">
         <v>0</v>
       </c>
       <c r="Y10" s="2">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="Z10" s="2">
         <v>0</v>
       </c>
       <c r="AA10" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>90</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="2">
         <v>50</v>
       </c>
-      <c r="AB10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>100</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="2">
-        <v>80</v>
-      </c>
       <c r="AJ10" s="2">
         <v>0</v>
       </c>
@@ -25178,7 +25219,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV10" s="3">
         <v>0</v>
@@ -25190,356 +25231,356 @@
         <v>30</v>
       </c>
       <c r="AY10" s="14" t="s">
-        <v>336</v>
+        <v>257</v>
       </c>
       <c r="AZ10" s="2">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="BA10" s="5" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="BB10" s="4" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="BC10" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:55" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21">
+    <row r="11" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="2">
         <f t="shared" si="1"/>
         <v>30009</v>
       </c>
-      <c r="C11" s="21">
-        <v>0</v>
-      </c>
-      <c r="D11" s="21">
-        <v>0</v>
-      </c>
-      <c r="E11" s="21">
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
         <v>15</v>
       </c>
-      <c r="F11" s="21">
-        <v>0</v>
-      </c>
-      <c r="G11" s="21">
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
         <v>1</v>
       </c>
-      <c r="H11" s="21">
-        <v>0</v>
-      </c>
-      <c r="I11" s="21">
-        <v>0</v>
-      </c>
-      <c r="J11" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="L11" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="M11" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="N11" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="O11" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="P11" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q11" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="R11" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="S11" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="T11" s="21">
-        <v>0</v>
-      </c>
-      <c r="U11" s="21">
+      <c r="V11" s="2">
         <v>1</v>
       </c>
-      <c r="V11" s="21">
-        <v>1</v>
-      </c>
-      <c r="W11" s="21">
-        <v>2700</v>
-      </c>
-      <c r="X11" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="21">
+      <c r="W11" s="2">
+        <v>8000</v>
+      </c>
+      <c r="X11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>180</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2">
+        <v>50</v>
+      </c>
+      <c r="AB11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>100</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="2">
         <v>80</v>
       </c>
-      <c r="Z11" s="21">
-        <v>150</v>
-      </c>
-      <c r="AA11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="21">
-        <v>200</v>
-      </c>
-      <c r="AE11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="21">
-        <v>50</v>
-      </c>
-      <c r="AJ11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL11" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM11" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN11" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO11" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AU11" s="21">
-        <v>10</v>
-      </c>
-      <c r="AV11" s="22">
-        <v>0</v>
-      </c>
-      <c r="AW11" s="22">
-        <v>0</v>
-      </c>
-      <c r="AX11" s="21">
+      <c r="AJ11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="2">
+        <v>12</v>
+      </c>
+      <c r="AV11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AX11" s="2">
         <v>30</v>
       </c>
-      <c r="AY11" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="AZ11" s="21">
+      <c r="AY11" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="AZ11" s="2">
         <v>23</v>
       </c>
-      <c r="BA11" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="BB11" s="25" t="s">
-        <v>368</v>
-      </c>
-      <c r="BC11" s="22">
+      <c r="BA11" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="BB11" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="BC11" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
+    <row r="12" spans="1:55" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="21">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="21">
         <f t="shared" si="1"/>
         <v>30010</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>18</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="T12" s="2">
-        <v>0</v>
-      </c>
-      <c r="U12" s="2">
+      <c r="C12" s="21">
+        <v>0</v>
+      </c>
+      <c r="D12" s="21">
+        <v>0</v>
+      </c>
+      <c r="E12" s="21">
+        <v>15</v>
+      </c>
+      <c r="F12" s="21">
+        <v>0</v>
+      </c>
+      <c r="G12" s="21">
         <v>1</v>
       </c>
-      <c r="V12" s="2">
+      <c r="H12" s="21">
+        <v>0</v>
+      </c>
+      <c r="I12" s="21">
+        <v>0</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="N12" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="O12" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="P12" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="R12" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="S12" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="T12" s="21">
+        <v>0</v>
+      </c>
+      <c r="U12" s="21">
         <v>1</v>
       </c>
-      <c r="W12" s="2">
-        <v>5000</v>
-      </c>
-      <c r="X12" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="2">
-        <v>180</v>
-      </c>
-      <c r="Z12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="2">
-        <v>40</v>
-      </c>
-      <c r="AB12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="2">
-        <v>90</v>
-      </c>
-      <c r="AD12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="2">
+      <c r="V12" s="21">
+        <v>1</v>
+      </c>
+      <c r="W12" s="21">
+        <v>2700</v>
+      </c>
+      <c r="X12" s="21">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="21">
         <v>80</v>
       </c>
-      <c r="AJ12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU12" s="2">
-        <v>13</v>
-      </c>
-      <c r="AV12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AX12" s="2">
+      <c r="Z12" s="21">
+        <v>150</v>
+      </c>
+      <c r="AA12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="21">
+        <v>200</v>
+      </c>
+      <c r="AE12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="21">
+        <v>50</v>
+      </c>
+      <c r="AJ12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL12" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM12" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN12" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO12" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="21">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="21">
+        <v>10</v>
+      </c>
+      <c r="AV12" s="22">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="22">
+        <v>0</v>
+      </c>
+      <c r="AX12" s="21">
         <v>30</v>
       </c>
-      <c r="AY12" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="AZ12" s="2">
+      <c r="AY12" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="AZ12" s="21">
         <v>23</v>
       </c>
-      <c r="BA12" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="BB12" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="BC12" s="3">
+      <c r="BA12" s="24" t="s">
+        <v>327</v>
+      </c>
+      <c r="BB12" s="25" t="s">
+        <v>368</v>
+      </c>
+      <c r="BC12" s="22">
         <v>0</v>
       </c>
     </row>
@@ -25574,10 +25615,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>7</v>
+        <v>318</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>7</v>
@@ -25601,7 +25642,7 @@
         <v>7</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>322</v>
+        <v>7</v>
       </c>
       <c r="T13" s="2">
         <v>0</v>
@@ -25613,25 +25654,25 @@
         <v>1</v>
       </c>
       <c r="W13" s="2">
-        <v>2300</v>
+        <v>5000</v>
       </c>
       <c r="X13" s="2">
         <v>0</v>
       </c>
       <c r="Y13" s="2">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="Z13" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB13" s="2">
         <v>0</v>
       </c>
       <c r="AC13" s="2">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AD13" s="2">
         <v>0</v>
@@ -25697,16 +25738,16 @@
         <v>30</v>
       </c>
       <c r="AY13" s="14" t="s">
-        <v>264</v>
+        <v>336</v>
       </c>
       <c r="AZ13" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BA13" s="5" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="BB13" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="BC13" s="3">
         <v>0</v>
@@ -25728,7 +25769,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -25743,10 +25784,10 @@
         <v>0</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>315</v>
+        <v>7</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>7</v>
@@ -25770,7 +25811,7 @@
         <v>7</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>7</v>
+        <v>322</v>
       </c>
       <c r="T14" s="2">
         <v>0</v>
@@ -25782,44 +25823,44 @@
         <v>1</v>
       </c>
       <c r="W14" s="2">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="X14" s="2">
         <v>0</v>
       </c>
       <c r="Y14" s="2">
+        <v>60</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>30</v>
+      </c>
+      <c r="AA14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>130</v>
+      </c>
+      <c r="AD14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="2">
         <v>80</v>
       </c>
-      <c r="Z14" s="2">
-        <v>230</v>
-      </c>
-      <c r="AA14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="2">
-        <v>120</v>
-      </c>
-      <c r="AE14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="2">
-        <v>50</v>
-      </c>
       <c r="AJ14" s="2">
         <v>0</v>
       </c>
@@ -25854,7 +25895,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV14" s="3">
         <v>0</v>
@@ -25866,16 +25907,16 @@
         <v>30</v>
       </c>
       <c r="AY14" s="14" t="s">
-        <v>331</v>
+        <v>264</v>
       </c>
       <c r="AZ14" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA14" s="5" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="BB14" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="BC14" s="3">
         <v>0</v>
@@ -25897,7 +25938,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
@@ -25912,10 +25953,10 @@
         <v>0</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>381</v>
+        <v>314</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>380</v>
+        <v>315</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>7</v>
@@ -25951,55 +25992,55 @@
         <v>1</v>
       </c>
       <c r="W15" s="2">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="X15" s="2">
         <v>0</v>
       </c>
       <c r="Y15" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="Z15" s="2">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="AA15" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="2">
         <v>0</v>
       </c>
       <c r="AC15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="2">
+        <v>120</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="2">
         <v>50</v>
       </c>
-      <c r="AD15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="2">
-        <v>90</v>
-      </c>
       <c r="AJ15" s="2">
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="s">
-        <v>384</v>
+        <v>7</v>
       </c>
       <c r="AL15" s="3" t="s">
-        <v>379</v>
+        <v>7</v>
       </c>
       <c r="AM15" s="3" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="AN15" s="3" t="s">
         <v>7</v>
@@ -26008,13 +26049,13 @@
         <v>7</v>
       </c>
       <c r="AP15" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ15" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR15" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS15" s="2">
         <v>0</v>
@@ -26023,7 +26064,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AV15" s="3">
         <v>0</v>
@@ -26035,16 +26076,16 @@
         <v>30</v>
       </c>
       <c r="AY15" s="14" t="s">
-        <v>264</v>
+        <v>331</v>
       </c>
       <c r="AZ15" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA15" s="5" t="s">
-        <v>382</v>
+        <v>316</v>
       </c>
       <c r="BB15" s="4" t="s">
-        <v>383</v>
+        <v>332</v>
       </c>
       <c r="BC15" s="3">
         <v>0</v>
@@ -26081,10 +26122,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>7</v>
@@ -26126,19 +26167,19 @@
         <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="Z16" s="2">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="AA16" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AB16" s="2">
         <v>0</v>
       </c>
       <c r="AC16" s="2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AD16" s="2">
         <v>0</v>
@@ -26156,7 +26197,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="2">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AJ16" s="2">
         <v>0</v>
@@ -26165,28 +26206,28 @@
         <v>384</v>
       </c>
       <c r="AL16" s="3" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AM16" s="3" t="s">
         <v>105</v>
       </c>
       <c r="AN16" s="3" t="s">
-        <v>379</v>
+        <v>7</v>
       </c>
       <c r="AO16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AP16" s="3">
+      <c r="AP16" s="2">
+        <v>10</v>
+      </c>
+      <c r="AQ16" s="2">
         <v>20</v>
       </c>
-      <c r="AQ16" s="3">
-        <v>50</v>
-      </c>
-      <c r="AR16" s="3">
-        <v>30</v>
-      </c>
-      <c r="AS16" s="3">
+      <c r="AR16" s="2">
         <v>20</v>
+      </c>
+      <c r="AS16" s="2">
+        <v>0</v>
       </c>
       <c r="AT16" s="2">
         <v>0</v>
@@ -26210,10 +26251,10 @@
         <v>16</v>
       </c>
       <c r="BA16" s="5" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="BB16" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="BC16" s="3">
         <v>0</v>
@@ -26221,21 +26262,21 @@
     </row>
     <row r="17" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <f t="shared" ref="B17" si="3">(ROW()-2)+30000</f>
+        <f t="shared" si="1"/>
         <v>30015</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2">
-        <v>9999</v>
+        <v>30</v>
       </c>
       <c r="F17" s="2">
         <v>0</v>
@@ -26250,10 +26291,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>20</v>
+        <v>386</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>7</v>
+        <v>385</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>7</v>
@@ -26277,7 +26318,7 @@
         <v>7</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="T17" s="2">
         <v>0</v>
@@ -26289,25 +26330,25 @@
         <v>1</v>
       </c>
       <c r="W17" s="2">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="X17" s="2">
         <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="Z17" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA17" s="2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB17" s="2">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AC17" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AD17" s="2">
         <v>0</v>
@@ -26325,66 +26366,235 @@
         <v>0</v>
       </c>
       <c r="AI17" s="2">
+        <v>60</v>
+      </c>
+      <c r="AJ17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="AL17" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="AM17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN17" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="AO17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP17" s="3">
+        <v>20</v>
+      </c>
+      <c r="AQ17" s="3">
         <v>50</v>
       </c>
-      <c r="AJ17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS17" s="2">
-        <v>0</v>
+      <c r="AR17" s="3">
+        <v>30</v>
+      </c>
+      <c r="AS17" s="3">
+        <v>20</v>
       </c>
       <c r="AT17" s="2">
         <v>0</v>
       </c>
       <c r="AU17" s="2">
-        <v>5</v>
-      </c>
-      <c r="AV17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW17" s="2">
+        <v>10</v>
+      </c>
+      <c r="AV17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="3">
         <v>0</v>
       </c>
       <c r="AX17" s="2">
         <v>30</v>
       </c>
       <c r="AY17" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="AZ17" s="2">
+        <v>16</v>
+      </c>
+      <c r="BA17" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="BB17" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="BC17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:55" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <f t="shared" ref="B18" si="3">(ROW()-2)+30000</f>
+        <v>30016</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <v>9999</v>
+      </c>
+      <c r="E18" s="2">
+        <v>9999</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T18" s="2">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2">
+        <v>1</v>
+      </c>
+      <c r="W18" s="2">
+        <v>300</v>
+      </c>
+      <c r="X18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="2">
+        <v>54</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="2">
+        <v>50</v>
+      </c>
+      <c r="AJ18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="2">
+        <v>5</v>
+      </c>
+      <c r="AV18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX18" s="2">
+        <v>30</v>
+      </c>
+      <c r="AY18" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="AZ17" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA17" s="5" t="s">
+      <c r="AZ18" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="BB17" s="4" t="s">
+      <c r="BB18" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BC17" s="2">
+      <c r="BC18" s="2">
         <v>1</v>
       </c>
     </row>
